--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Barça.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Barça.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2071</v>
+        <v>2371.16</v>
       </c>
       <c r="C2" t="n">
-        <v>2066.42</v>
+        <v>2366.78</v>
       </c>
       <c r="D2" t="n">
-        <v>120.2078957811094</v>
+        <v>121.2195472329494</v>
       </c>
       <c r="E2" t="n">
-        <v>110.2389640053813</v>
+        <v>110.6144212812344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5977765108323831</v>
+        <v>0.601593625498008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1406926406926407</v>
+        <v>0.1406931305541725</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2795321637426901</v>
+        <v>0.2871794871794872</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2206385404789054</v>
+        <v>0.225597609561753</v>
       </c>
       <c r="J2" t="n">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="K2" t="n">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="L2" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N2" t="n">
-        <v>730</v>
+        <v>864</v>
       </c>
       <c r="O2" t="n">
-        <v>960</v>
+        <v>1134</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5473204104903079</v>
+        <v>0.5647410358565738</v>
       </c>
       <c r="Q2" t="n">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="R2" t="n">
-        <v>302</v>
+        <v>341</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1721778791334093</v>
+        <v>0.1698207171314741</v>
       </c>
       <c r="T2" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="U2" t="n">
-        <v>281</v>
+        <v>327</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1602052451539339</v>
+        <v>0.1628486055776892</v>
       </c>
       <c r="W2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="X2" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08323831242873432</v>
+        <v>0.08017928286852589</v>
       </c>
       <c r="Z2" t="n">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="AA2" t="n">
-        <v>590</v>
+        <v>659</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3363740022805017</v>
+        <v>0.3281872509960159</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7604166666666666</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5298013245033113</v>
+        <v>0.5366568914956011</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4199288256227758</v>
+        <v>0.4281345565749236</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.4472049689440994</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3711864406779661</v>
+        <v>0.370257966616085</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.520833333333333</v>
+        <v>1.523809523809524</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.8398576512455516</v>
+        <v>0.8562691131498471</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.161684782608696</v>
+        <v>1.15609756097561</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7375690607734806</v>
+        <v>0.7457627118644068</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.03347280334728</v>
+        <v>1.053571428571429</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.716216216216216</v>
+        <v>1.709302325581395</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.421538461538462</v>
+        <v>1.407506702412869</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.396923076923077</v>
+        <v>5.383378016085791</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.818461538461539</v>
+        <v>6.79088471849866</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.96428571428574</v>
+        <v>74.09875000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>73.80071428571429</v>
+        <v>73.96187499999999</v>
       </c>
       <c r="D3" t="n">
-        <v>120.2078957811093</v>
+        <v>121.2195472329494</v>
       </c>
       <c r="E3" t="n">
-        <v>110.2389640053813</v>
+        <v>110.6144212812344</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5977765108323831</v>
+        <v>0.601593625498008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1406926406926407</v>
+        <v>0.1406931305541725</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2795321637426901</v>
+        <v>0.2871794871794872</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2206385404789054</v>
+        <v>0.225597609561753</v>
       </c>
       <c r="J3" t="n">
-        <v>9.535714285714286</v>
+        <v>9.625</v>
       </c>
       <c r="K3" t="n">
-        <v>8.821428571428571</v>
+        <v>9.21875</v>
       </c>
       <c r="L3" t="n">
-        <v>4.535714285714286</v>
+        <v>4.59375</v>
       </c>
       <c r="M3" t="n">
-        <v>10.67857142857143</v>
+        <v>10.8125</v>
       </c>
       <c r="N3" t="n">
-        <v>26.07142857142857</v>
+        <v>27</v>
       </c>
       <c r="O3" t="n">
-        <v>34.28571428571428</v>
+        <v>35.4375</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5473204104903079</v>
+        <v>0.5647410358565738</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.714285714285714</v>
+        <v>5.71875</v>
       </c>
       <c r="R3" t="n">
-        <v>10.78571428571429</v>
+        <v>10.65625</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1721778791334094</v>
+        <v>0.1698207171314741</v>
       </c>
       <c r="T3" t="n">
-        <v>4.214285714285714</v>
+        <v>4.375</v>
       </c>
       <c r="U3" t="n">
-        <v>10.03571428571429</v>
+        <v>10.21875</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1602052451539339</v>
+        <v>0.1628486055776892</v>
       </c>
       <c r="W3" t="n">
-        <v>2.357142857142857</v>
+        <v>2.25</v>
       </c>
       <c r="X3" t="n">
-        <v>5.214285714285714</v>
+        <v>5.03125</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08323831242873433</v>
+        <v>0.08017928286852589</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.821428571428571</v>
+        <v>7.625</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.07142857142857</v>
+        <v>20.59375</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3363740022805017</v>
+        <v>0.3281872509960159</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7604166666666667</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5298013245033112</v>
+        <v>0.5366568914956011</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4199288256227758</v>
+        <v>0.4281345565749236</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.4472049689440994</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3711864406779661</v>
+        <v>0.370257966616085</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.520833333333333</v>
+        <v>1.523809523809524</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8398576512455516</v>
+        <v>0.8562691131498471</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.161684782608696</v>
+        <v>1.15609756097561</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7375690607734807</v>
+        <v>0.7457627118644068</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.03347280334728</v>
+        <v>1.053571428571429</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.716216216216216</v>
+        <v>1.709302325581395</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.421538461538461</v>
+        <v>1.407506702412869</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.396923076923076</v>
+        <v>5.383378016085791</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.818461538461538</v>
+        <v>6.79088471849866</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2061.84</v>
+        <v>2362.4</v>
       </c>
       <c r="C4" t="n">
-        <v>2066.42</v>
+        <v>2366.78</v>
       </c>
       <c r="D4" t="n">
-        <v>110.2389640053813</v>
+        <v>110.6144212812344</v>
       </c>
       <c r="E4" t="n">
-        <v>120.2078957811094</v>
+        <v>121.2195472329494</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5459667852906287</v>
+        <v>0.5488372093023256</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1577452022798975</v>
+        <v>0.1571896171119738</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2580287929125138</v>
+        <v>0.2533460803059274</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2591933570581257</v>
+        <v>0.255297157622739</v>
       </c>
       <c r="J4" t="n">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="K4" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="L4" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="M4" t="n">
-        <v>338</v>
+        <v>386</v>
       </c>
       <c r="N4" t="n">
-        <v>793</v>
+        <v>890</v>
       </c>
       <c r="O4" t="n">
-        <v>1025</v>
+        <v>1160</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6079478054567022</v>
+        <v>0.599483204134367</v>
       </c>
       <c r="Q4" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="R4" t="n">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1654804270462633</v>
+        <v>0.1643410852713178</v>
       </c>
       <c r="T4" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="U4" t="n">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1548042704626335</v>
+        <v>0.1514211886304909</v>
       </c>
       <c r="W4" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="X4" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09786476868327403</v>
+        <v>0.09819121447028424</v>
       </c>
       <c r="Z4" t="n">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="AA4" t="n">
-        <v>517</v>
+        <v>609</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3066429418742586</v>
+        <v>0.3147286821705426</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7736585365853659</v>
+        <v>0.7672413793103449</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4874551971326165</v>
+        <v>0.4654088050314465</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3256704980842912</v>
+        <v>0.3447098976109215</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3393939393939394</v>
+        <v>0.3473684210526316</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3346228239845261</v>
+        <v>0.3481116584564861</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.547317073170732</v>
+        <v>1.53448275862069</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6513409961685823</v>
+        <v>0.689419795221843</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.00733137829912</v>
+        <v>1.043804755944931</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8430769230769231</v>
+        <v>0.8471849865951743</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9227467811158798</v>
+        <v>0.9245283018867925</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.63768115942029</v>
+        <v>1.670886075949367</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.298342541436464</v>
+        <v>1.268765133171913</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.657458563535911</v>
+        <v>4.685230024213075</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.955801104972376</v>
+        <v>5.953995157384988</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.63714285714285</v>
+        <v>73.82499999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>73.80071428571429</v>
+        <v>73.96187499999999</v>
       </c>
       <c r="D5" t="n">
-        <v>110.2389640053813</v>
+        <v>110.6144212812344</v>
       </c>
       <c r="E5" t="n">
-        <v>120.2078957811093</v>
+        <v>121.2195472329494</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5459667852906288</v>
+        <v>0.5488372093023256</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1577452022798975</v>
+        <v>0.1571896171119738</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2580287929125138</v>
+        <v>0.2533460803059274</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2591933570581258</v>
+        <v>0.255297157622739</v>
       </c>
       <c r="J5" t="n">
-        <v>9.785714285714286</v>
+        <v>9.875</v>
       </c>
       <c r="K5" t="n">
-        <v>7.678571428571429</v>
+        <v>7.65625</v>
       </c>
       <c r="L5" t="n">
-        <v>4.035714285714286</v>
+        <v>4.125</v>
       </c>
       <c r="M5" t="n">
-        <v>12.07142857142857</v>
+        <v>12.0625</v>
       </c>
       <c r="N5" t="n">
-        <v>28.32142857142857</v>
+        <v>27.8125</v>
       </c>
       <c r="O5" t="n">
-        <v>36.60714285714285</v>
+        <v>36.25</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6079478054567022</v>
+        <v>0.599483204134367</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.857142857142857</v>
+        <v>4.625</v>
       </c>
       <c r="R5" t="n">
-        <v>9.964285714285714</v>
+        <v>9.9375</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1654804270462633</v>
+        <v>0.1643410852713178</v>
       </c>
       <c r="T5" t="n">
-        <v>3.035714285714286</v>
+        <v>3.15625</v>
       </c>
       <c r="U5" t="n">
-        <v>9.321428571428571</v>
+        <v>9.15625</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1548042704626335</v>
+        <v>0.1514211886304909</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>2.0625</v>
       </c>
       <c r="X5" t="n">
-        <v>5.892857142857143</v>
+        <v>5.9375</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09786476868327404</v>
+        <v>0.09819121447028424</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.178571428571429</v>
+        <v>6.625</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.46428571428572</v>
+        <v>19.03125</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3066429418742587</v>
+        <v>0.3147286821705426</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.773658536585366</v>
+        <v>0.7672413793103449</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4874551971326165</v>
+        <v>0.4654088050314465</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3256704980842912</v>
+        <v>0.3447098976109215</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3393939393939394</v>
+        <v>0.3473684210526316</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3346228239845261</v>
+        <v>0.3481116584564861</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.547317073170732</v>
+        <v>1.53448275862069</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6513409961685823</v>
+        <v>0.689419795221843</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.00733137829912</v>
+        <v>1.043804755944931</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8430769230769231</v>
+        <v>0.8471849865951743</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9227467811158799</v>
+        <v>0.9245283018867925</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.63768115942029</v>
+        <v>1.670886075949367</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.298342541436464</v>
+        <v>1.268765133171913</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.657458563535911</v>
+        <v>4.685230024213075</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.955801104972376</v>
+        <v>5.953995157384988</v>
       </c>
     </row>
     <row r="7">
@@ -1419,40 +1419,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>321</v>
+        <v>396</v>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="H8" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I8" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K8" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="L8" t="n">
         <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N8" t="n">
         <v>13</v>
@@ -1461,114 +1461,114 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="R8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="S8" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="T8" t="n">
-        <v>308</v>
+        <v>372</v>
       </c>
       <c r="U8" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="W8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="Z8" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.87</v>
+        <v>0.889</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.348</v>
+        <v>0.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.507</v>
+        <v>0.505</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AK8" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AL8" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.423</v>
+        <v>0.45</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>614:22</t>
+          <t>707:50</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>291.76</v>
+        <v>351.28</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.597</v>
+        <v>0.612</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.63</v>
+        <v>0.644</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.1</v>
+        <v>1.127</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.127</v>
+        <v>0.125</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.195</v>
+        <v>0.189</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.351</v>
+        <v>1.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9">
@@ -1578,64 +1578,64 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>32</v>
+      </c>
+      <c r="C9" t="n">
+        <v>143</v>
+      </c>
+      <c r="D9" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" t="n">
+        <v>44</v>
+      </c>
+      <c r="F9" t="n">
         <v>28</v>
       </c>
-      <c r="C9" t="n">
-        <v>107</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="G9" t="n">
+        <v>65</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" t="n">
+        <v>57</v>
+      </c>
+      <c r="K9" t="n">
+        <v>34</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>32</v>
+      </c>
+      <c r="R9" t="n">
+        <v>63</v>
+      </c>
+      <c r="S9" t="n">
+        <v>26</v>
+      </c>
+      <c r="T9" t="n">
+        <v>141</v>
+      </c>
+      <c r="U9" t="n">
         <v>17</v>
-      </c>
-      <c r="E9" t="n">
-        <v>34</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22</v>
-      </c>
-      <c r="G9" t="n">
-        <v>55</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>50</v>
-      </c>
-      <c r="K9" t="n">
-        <v>27</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>17</v>
-      </c>
-      <c r="N9" t="n">
-        <v>9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>31</v>
-      </c>
-      <c r="R9" t="n">
-        <v>57</v>
-      </c>
-      <c r="S9" t="n">
-        <v>21</v>
-      </c>
-      <c r="T9" t="n">
-        <v>95</v>
-      </c>
-      <c r="U9" t="n">
-        <v>11</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
@@ -1647,31 +1647,31 @@
         <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.536</v>
+        <v>0.61</v>
       </c>
       <c r="AB9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.545</v>
+        <v>0.583</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.6</v>
+        <v>0.429</v>
       </c>
       <c r="AH9" t="n">
         <v>2</v>
@@ -1683,51 +1683,51 @@
         <v>0.333</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.408</v>
+        <v>0.441</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>350:53</t>
+          <t>421:08</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>124.4</v>
+        <v>148.04</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.606</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.573</v>
+        <v>0.616</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.86</v>
+        <v>0.966</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.249</v>
+        <v>0.216</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.079</v>
+        <v>0.101</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.613</v>
+        <v>1.781</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.172</v>
+        <v>0.17</v>
       </c>
       <c r="AW9" t="n">
         <v>0.019</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.095</v>
+        <v>0.099</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="10">
@@ -1737,40 +1737,40 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>26</v>
+      </c>
+      <c r="C10" t="n">
+        <v>181</v>
+      </c>
+      <c r="D10" t="n">
+        <v>42</v>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>27</v>
+      </c>
+      <c r="G10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I10" t="n">
         <v>22</v>
       </c>
-      <c r="C10" t="n">
-        <v>155</v>
-      </c>
-      <c r="D10" t="n">
-        <v>38</v>
-      </c>
-      <c r="E10" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22</v>
-      </c>
-      <c r="G10" t="n">
-        <v>61</v>
-      </c>
-      <c r="H10" t="n">
-        <v>13</v>
-      </c>
-      <c r="I10" t="n">
-        <v>18</v>
-      </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L10" t="n">
         <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1779,22 +1779,22 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>163</v>
+      </c>
+      <c r="U10" t="n">
         <v>22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>140</v>
-      </c>
-      <c r="U10" t="n">
-        <v>17</v>
       </c>
       <c r="V10" t="n">
         <v>16</v>
@@ -1806,87 +1806,87 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="AB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE10" t="n">
         <v>4</v>
       </c>
-      <c r="AC10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3</v>
-      </c>
       <c r="AF10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.481</v>
+        <v>0.516</v>
       </c>
       <c r="AK10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.265</v>
+        <v>0.282</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>451:39</t>
+          <t>526:54</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>129.92</v>
+        <v>147.68</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.652</v>
+        <v>0.672</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.193</v>
+        <v>1.226</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.117</v>
+        <v>0.128</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.364</v>
+        <v>1.231</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.139</v>
+        <v>0.135</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.041</v>
+        <v>0.035</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.082</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="11">
@@ -1896,67 +1896,67 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C11" t="n">
+        <v>130</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" t="n">
+        <v>37</v>
+      </c>
+      <c r="F11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G11" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" t="n">
+        <v>22</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>58</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" t="n">
         <v>14</v>
       </c>
-      <c r="C11" t="n">
-        <v>117</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23</v>
-      </c>
-      <c r="E11" t="n">
-        <v>33</v>
-      </c>
-      <c r="F11" t="n">
-        <v>21</v>
-      </c>
-      <c r="G11" t="n">
-        <v>50</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>50</v>
-      </c>
-      <c r="L11" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>12</v>
-      </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T11" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W11" t="n">
         <v>8</v>
@@ -1965,22 +1965,22 @@
         <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="Z11" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.758</v>
+        <v>0.705</v>
       </c>
       <c r="AB11" t="n">
         <v>5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.556</v>
+        <v>0.5</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2001,51 +2001,51 @@
         <v>0.312</v>
       </c>
       <c r="AK11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.471</v>
+        <v>0.419</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>313:04</t>
+          <t>384:58</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>92.16</v>
+        <v>110.68</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.657</v>
+        <v>0.609</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.656</v>
+        <v>0.615</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.27</v>
+        <v>1.175</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.033</v>
+        <v>0.045</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.096</v>
+        <v>0.135</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.143</v>
+        <v>0.139</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.198</v>
+        <v>0.184</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="12">
@@ -2195,16 +2195,16 @@
         <v>3.714</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.14</v>
+        <v>0.138</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="13">
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="H13" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I13" t="n">
+        <v>31</v>
+      </c>
+      <c r="J13" t="n">
+        <v>49</v>
+      </c>
+      <c r="K13" t="n">
         <v>27</v>
-      </c>
-      <c r="J13" t="n">
-        <v>38</v>
-      </c>
-      <c r="K13" t="n">
-        <v>25</v>
       </c>
       <c r="L13" t="n">
         <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -2256,114 +2256,114 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="S13" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="T13" t="n">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="U13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V13" t="n">
         <v>12</v>
       </c>
       <c r="W13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Z13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AK13" t="n">
         <v>41</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>35</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>39</v>
-      </c>
       <c r="AL13" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.419</v>
+        <v>0.398</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>409:04</t>
+          <t>475:50</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>213.88</v>
+        <v>245.64</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.575</v>
+        <v>0.571</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.594</v>
+        <v>0.592</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.066</v>
+        <v>1.054</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.103</v>
+        <v>0.11</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.117</v>
+        <v>0.122</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.727</v>
+        <v>1.815</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.254</v>
+        <v>0.249</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.076</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.046</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="14">
@@ -2513,16 +2513,16 @@
         <v>2.647</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="AW14" t="n">
         <v>0.028</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.106</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="15">
@@ -2532,100 +2532,100 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>32</v>
+      </c>
+      <c r="C15" t="n">
+        <v>280</v>
+      </c>
+      <c r="D15" t="n">
+        <v>102</v>
+      </c>
+      <c r="E15" t="n">
+        <v>150</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>76</v>
+      </c>
+      <c r="I15" t="n">
+        <v>108</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19</v>
+      </c>
+      <c r="K15" t="n">
+        <v>96</v>
+      </c>
+      <c r="L15" t="n">
+        <v>40</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18</v>
+      </c>
+      <c r="N15" t="n">
+        <v>27</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>31</v>
+      </c>
+      <c r="R15" t="n">
+        <v>55</v>
+      </c>
+      <c r="S15" t="n">
+        <v>105</v>
+      </c>
+      <c r="T15" t="n">
+        <v>417</v>
+      </c>
+      <c r="U15" t="n">
         <v>28</v>
       </c>
-      <c r="C15" t="n">
-        <v>235</v>
-      </c>
-      <c r="D15" t="n">
-        <v>88</v>
-      </c>
-      <c r="E15" t="n">
-        <v>130</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>84</v>
-      </c>
-      <c r="J15" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" t="n">
-        <v>76</v>
-      </c>
-      <c r="L15" t="n">
-        <v>35</v>
-      </c>
-      <c r="M15" t="n">
-        <v>14</v>
-      </c>
-      <c r="N15" t="n">
-        <v>24</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>29</v>
-      </c>
-      <c r="R15" t="n">
-        <v>46</v>
-      </c>
-      <c r="S15" t="n">
-        <v>90</v>
-      </c>
-      <c r="T15" t="n">
-        <v>345</v>
-      </c>
-      <c r="U15" t="n">
-        <v>18</v>
-      </c>
       <c r="V15" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="W15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="n">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="Z15" t="n">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.788</v>
+        <v>0.772</v>
       </c>
       <c r="AB15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AC15" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.425</v>
+        <v>0.477</v>
       </c>
       <c r="AE15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.389</v>
+        <v>0.381</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2640,48 +2640,48 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>461:46</t>
+          <t>532:37</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>196.96</v>
+        <v>230.52</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.672</v>
+        <v>0.671</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.7</v>
+        <v>0.702</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.193</v>
+        <v>1.215</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.147</v>
+        <v>0.134</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.483</v>
+        <v>0.613</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.207</v>
+        <v>0.209</v>
       </c>
       <c r="AW15" t="n">
         <v>0.099</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.204</v>
+        <v>0.221</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
+        <v>13</v>
+      </c>
+      <c r="J16" t="n">
+        <v>21</v>
+      </c>
+      <c r="K16" t="n">
+        <v>18</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
@@ -2733,26 +2733,26 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="S16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T16" t="n">
+        <v>56</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
-        <v>8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
@@ -2760,87 +2760,87 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AB16" t="n">
         <v>3</v>
       </c>
-      <c r="Z16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
       </c>
       <c r="AF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
         <v>2</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AL16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>121:27</t>
+        </is>
+      </c>
+      <c r="AO16" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="AP16" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>41:20</t>
-        </is>
-      </c>
-      <c r="AO16" t="n">
-        <v>15.88</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>0.414</v>
+        <v>0.532</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.315</v>
+        <v>0.267</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.1</v>
+        <v>0.267</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.4</v>
+        <v>1.615</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.186</v>
+        <v>0.194</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.12</v>
+        <v>0.181</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17">
@@ -2850,16 +2850,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2868,49 +2868,49 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I17" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>49</v>
+      </c>
+      <c r="L17" t="n">
+        <v>45</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
         <v>18</v>
       </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>36</v>
-      </c>
-      <c r="L17" t="n">
-        <v>34</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>9</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R17" t="n">
+        <v>35</v>
+      </c>
+      <c r="S17" t="n">
         <v>26</v>
       </c>
-      <c r="S17" t="n">
-        <v>20</v>
-      </c>
       <c r="T17" t="n">
-        <v>154</v>
+        <v>221</v>
       </c>
       <c r="U17" t="n">
         <v>14</v>
       </c>
       <c r="V17" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="W17" t="n">
         <v>3</v>
@@ -2919,31 +2919,31 @@
         <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="Z17" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.746</v>
+        <v>0.784</v>
       </c>
       <c r="AB17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.714</v>
+        <v>0.619</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.5</v>
+        <v>0.538</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2965,41 +2965,41 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>187:59</t>
+          <t>267:19</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>86.92</v>
+        <v>124</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.696</v>
+        <v>0.711</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.715</v>
+        <v>0.731</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.266</v>
+        <v>1.274</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.115</v>
+        <v>0.129</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.203</v>
+        <v>0.206</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AV17" t="n">
         <v>0.224</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.237</v>
+        <v>0.221</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.238</v>
+        <v>0.224</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="18">
@@ -3149,16 +3149,16 @@
         <v>2.227</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.252</v>
+        <v>0.251</v>
       </c>
       <c r="AW18" t="n">
         <v>0.025</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.091</v>
+        <v>0.09</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.057</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="19">
@@ -3308,16 +3308,16 @@
         <v>1.28</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.234</v>
+        <v>0.233</v>
       </c>
       <c r="AW19" t="n">
         <v>0.033</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.163</v>
+        <v>0.16</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.039</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="20">
@@ -3327,100 +3327,100 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>28</v>
+      </c>
+      <c r="C20" t="n">
+        <v>287</v>
+      </c>
+      <c r="D20" t="n">
+        <v>98</v>
+      </c>
+      <c r="E20" t="n">
+        <v>154</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>43</v>
+      </c>
+      <c r="H20" t="n">
+        <v>76</v>
+      </c>
+      <c r="I20" t="n">
+        <v>98</v>
+      </c>
+      <c r="J20" t="n">
+        <v>52</v>
+      </c>
+      <c r="K20" t="n">
+        <v>72</v>
+      </c>
+      <c r="L20" t="n">
+        <v>27</v>
+      </c>
+      <c r="M20" t="n">
+        <v>17</v>
+      </c>
+      <c r="N20" t="n">
+        <v>23</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>42</v>
+      </c>
+      <c r="R20" t="n">
+        <v>60</v>
+      </c>
+      <c r="S20" t="n">
+        <v>117</v>
+      </c>
+      <c r="T20" t="n">
+        <v>377</v>
+      </c>
+      <c r="U20" t="n">
+        <v>27</v>
+      </c>
+      <c r="V20" t="n">
+        <v>33</v>
+      </c>
+      <c r="W20" t="n">
+        <v>13</v>
+      </c>
+      <c r="X20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>141</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>189</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="AB20" t="n">
         <v>24</v>
       </c>
-      <c r="C20" t="n">
-        <v>242</v>
-      </c>
-      <c r="D20" t="n">
-        <v>79</v>
-      </c>
-      <c r="E20" t="n">
-        <v>123</v>
-      </c>
-      <c r="F20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" t="n">
-        <v>37</v>
-      </c>
-      <c r="H20" t="n">
-        <v>72</v>
-      </c>
-      <c r="I20" t="n">
-        <v>92</v>
-      </c>
-      <c r="J20" t="n">
-        <v>43</v>
-      </c>
-      <c r="K20" t="n">
-        <v>60</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="AC20" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF20" t="n">
         <v>18</v>
       </c>
-      <c r="M20" t="n">
-        <v>13</v>
-      </c>
-      <c r="N20" t="n">
-        <v>19</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>34</v>
-      </c>
-      <c r="R20" t="n">
-        <v>55</v>
-      </c>
-      <c r="S20" t="n">
-        <v>100</v>
-      </c>
-      <c r="T20" t="n">
-        <v>309</v>
-      </c>
-      <c r="U20" t="n">
-        <v>25</v>
-      </c>
-      <c r="V20" t="n">
-        <v>29</v>
-      </c>
-      <c r="W20" t="n">
-        <v>11</v>
-      </c>
-      <c r="X20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>124</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>165</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>39</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>11</v>
-      </c>
       <c r="AG20" t="n">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="AH20" t="n">
         <v>1</v>
@@ -3432,51 +3432,51 @@
         <v>0.167</v>
       </c>
       <c r="AK20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL20" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.097</v>
+        <v>0.108</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>486:03</t>
+          <t>575:06</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>234.48</v>
+        <v>282.12</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.531</v>
+        <v>0.536</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.604</v>
+        <v>0.598</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.032</v>
+        <v>1.017</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.145</v>
+        <v>0.149</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.45</v>
+        <v>0.386</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.265</v>
+        <v>1.238</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.049</v>
+        <v>0.062</v>
       </c>
       <c r="AX20" t="n">
         <v>0.153</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="21">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="n">
         <v>3</v>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3504,10 +3504,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3519,7 +3519,7 @@
         <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -3528,19 +3528,19 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
@@ -3549,28 +3549,28 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2</v>
       </c>
-      <c r="Z21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1</v>
-      </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3601,38 +3601,38 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>43:23</t>
+          <t>49:15</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>10.76</v>
+        <v>15.64</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.143</v>
+        <v>0.333</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.171</v>
+        <v>0.344</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.279</v>
+        <v>0.512</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.186</v>
+        <v>0.256</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.143</v>
+        <v>0.222</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.12</v>
+        <v>0.153</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.181</v>
+        <v>0.16</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.172</v>
+        <v>0.149</v>
       </c>
       <c r="AY21" t="n">
         <v>0.001</v>
@@ -3785,13 +3785,13 @@
         <v>0.667</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.217</v>
+        <v>0.216</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.245</v>
+        <v>0.242</v>
       </c>
       <c r="AY22" t="n">
         <v>0.002</v>
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>31</v>
+      </c>
+      <c r="C23" t="n">
+        <v>262</v>
+      </c>
+      <c r="D23" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" t="n">
+        <v>107</v>
+      </c>
+      <c r="F23" t="n">
+        <v>26</v>
+      </c>
+      <c r="G23" t="n">
+        <v>74</v>
+      </c>
+      <c r="H23" t="n">
+        <v>46</v>
+      </c>
+      <c r="I23" t="n">
+        <v>61</v>
+      </c>
+      <c r="J23" t="n">
+        <v>42</v>
+      </c>
+      <c r="K23" t="n">
+        <v>107</v>
+      </c>
+      <c r="L23" t="n">
+        <v>37</v>
+      </c>
+      <c r="M23" t="n">
         <v>27</v>
-      </c>
-      <c r="C23" t="n">
-        <v>230</v>
-      </c>
-      <c r="D23" t="n">
-        <v>58</v>
-      </c>
-      <c r="E23" t="n">
-        <v>90</v>
-      </c>
-      <c r="F23" t="n">
-        <v>25</v>
-      </c>
-      <c r="G23" t="n">
-        <v>67</v>
-      </c>
-      <c r="H23" t="n">
-        <v>39</v>
-      </c>
-      <c r="I23" t="n">
-        <v>52</v>
-      </c>
-      <c r="J23" t="n">
-        <v>37</v>
-      </c>
-      <c r="K23" t="n">
-        <v>90</v>
-      </c>
-      <c r="L23" t="n">
-        <v>35</v>
-      </c>
-      <c r="M23" t="n">
-        <v>24</v>
       </c>
       <c r="N23" t="n">
         <v>13</v>
@@ -3846,114 +3846,114 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R23" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S23" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="T23" t="n">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="U23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="W23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="Z23" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.772</v>
+        <v>0.78</v>
       </c>
       <c r="AB23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC23" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.581</v>
+        <v>0.556</v>
       </c>
       <c r="AE23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.421</v>
+        <v>0.435</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.615</v>
+        <v>0.586</v>
       </c>
       <c r="AK23" t="n">
         <v>9</v>
       </c>
       <c r="AL23" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>620:09</t>
+          <t>709:33</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>201.88</v>
+        <v>232.84</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.608</v>
+        <v>0.597</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.639</v>
+        <v>0.63</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.139</v>
+        <v>1.125</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.248</v>
+        <v>0.254</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.682</v>
+        <v>1.68</v>
       </c>
       <c r="AV23" t="n">
         <v>0.158</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.074</v>
+        <v>0.068</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.18</v>
+        <v>0.185</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="24">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -3978,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>2</v>
@@ -4017,7 +4017,7 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -4071,27 +4071,27 @@
         <v>1</v>
       </c>
       <c r="AL24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM24" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AO24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP24" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AO24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AQ24" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AS24" t="n">
         <v>0.5</v>
@@ -4100,19 +4100,19 @@
         <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.153</v>
+        <v>0.141</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.104</v>
+        <v>0.064</v>
       </c>
       <c r="AX24" t="n">
         <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="25">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4149,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L25" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4277,157 +4277,157 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2869</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>820</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="T26" t="n">
-        <v>38</v>
+        <v>3389</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1134</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>0.537</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>0.447</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>26</v>
+        <v>2651.16</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>0.602</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.082</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.408</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4436,157 +4436,157 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>2484</v>
+        <v>2618</v>
       </c>
       <c r="D27" t="n">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="E27" t="n">
-        <v>1018</v>
+        <v>1136</v>
       </c>
       <c r="F27" t="n">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="G27" t="n">
-        <v>736</v>
+        <v>799</v>
       </c>
       <c r="H27" t="n">
-        <v>387</v>
+        <v>494</v>
       </c>
       <c r="I27" t="n">
-        <v>525</v>
+        <v>635</v>
       </c>
       <c r="J27" t="n">
-        <v>462</v>
+        <v>524</v>
       </c>
       <c r="K27" t="n">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="L27" t="n">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="M27" t="n">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="N27" t="n">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>325</v>
+        <v>413</v>
       </c>
       <c r="Q27" t="n">
-        <v>299</v>
+        <v>386</v>
       </c>
       <c r="R27" t="n">
-        <v>584</v>
+        <v>693</v>
       </c>
       <c r="S27" t="n">
-        <v>605</v>
+        <v>649</v>
       </c>
       <c r="T27" t="n">
-        <v>2902</v>
+        <v>2841</v>
       </c>
       <c r="U27" t="n">
-        <v>267</v>
+        <v>316</v>
       </c>
       <c r="V27" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="W27" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="X27" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="n">
-        <v>730</v>
+        <v>890</v>
       </c>
       <c r="Z27" t="n">
-        <v>960</v>
+        <v>1160</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.76</v>
+        <v>0.767</v>
       </c>
       <c r="AB27" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="AC27" t="n">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.53</v>
+        <v>0.465</v>
       </c>
       <c r="AE27" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AF27" t="n">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.42</v>
+        <v>0.345</v>
       </c>
       <c r="AH27" t="n">
         <v>66</v>
       </c>
       <c r="AI27" t="n">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.452</v>
+        <v>0.347</v>
       </c>
       <c r="AK27" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AL27" t="n">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.371</v>
+        <v>0.348</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2310</v>
+        <v>2627.4</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.598</v>
+        <v>0.549</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.626</v>
+        <v>0.591</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.075</v>
+        <v>0.996</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.141</v>
+        <v>0.157</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.221</v>
+        <v>0.255</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.422</v>
+        <v>1.269</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.056</v>
+        <v>0.051</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.148</v>
+        <v>0.143</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4595,1592 +4595,1592 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>28</v>
-      </c>
-      <c r="C28" t="n">
-        <v>2278</v>
-      </c>
-      <c r="D28" t="n">
-        <v>577</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1004</v>
-      </c>
-      <c r="F28" t="n">
-        <v>229</v>
-      </c>
-      <c r="G28" t="n">
-        <v>682</v>
-      </c>
-      <c r="H28" t="n">
-        <v>437</v>
-      </c>
-      <c r="I28" t="n">
-        <v>561</v>
-      </c>
-      <c r="J28" t="n">
-        <v>470</v>
-      </c>
-      <c r="K28" t="n">
-        <v>616</v>
-      </c>
-      <c r="L28" t="n">
-        <v>233</v>
-      </c>
-      <c r="M28" t="n">
-        <v>171</v>
-      </c>
-      <c r="N28" t="n">
-        <v>130</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>362</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>338</v>
-      </c>
-      <c r="R28" t="n">
-        <v>607</v>
-      </c>
-      <c r="S28" t="n">
-        <v>577</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2502</v>
-      </c>
-      <c r="U28" t="n">
-        <v>274</v>
-      </c>
-      <c r="V28" t="n">
-        <v>215</v>
-      </c>
-      <c r="W28" t="n">
-        <v>113</v>
-      </c>
-      <c r="X28" t="n">
-        <v>69</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>793</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1025</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>136</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>279</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>261</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>56</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>165</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>173</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>517</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>5600:00</t>
-        </is>
-      </c>
-      <c r="AO28" t="n">
-        <v>2294.84</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.298</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
+          <t>#0 K. PUNTER (Per Game)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.567</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.067</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.533</v>
+      </c>
+      <c r="T29" t="n">
+        <v>372</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>23:35</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
+        <v>11.709</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.065</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#0 K. PUNTER (Per Game)</t>
+          <t>#2 J. MARCOS (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>12.346</v>
+        <v>4.469</v>
       </c>
       <c r="D30" t="n">
-        <v>2.308</v>
+        <v>0.75</v>
       </c>
       <c r="E30" t="n">
-        <v>4.269</v>
+        <v>1.375</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>0.875</v>
       </c>
       <c r="G30" t="n">
-        <v>4.615</v>
+        <v>2.031</v>
       </c>
       <c r="H30" t="n">
-        <v>1.731</v>
+        <v>0.344</v>
       </c>
       <c r="I30" t="n">
-        <v>2.077</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
-        <v>1.923</v>
+        <v>1.781</v>
       </c>
       <c r="K30" t="n">
-        <v>1.654</v>
+        <v>1.062</v>
       </c>
       <c r="L30" t="n">
-        <v>0.231</v>
+        <v>0.188</v>
       </c>
       <c r="M30" t="n">
-        <v>1.077</v>
+        <v>0.625</v>
       </c>
       <c r="N30" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.423</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.423</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>2.154</v>
+        <v>1.969</v>
       </c>
       <c r="S30" t="n">
-        <v>2.615</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="T30" t="n">
-        <v>308</v>
+        <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>1.462</v>
+        <v>0.531</v>
       </c>
       <c r="V30" t="n">
-        <v>0.654</v>
+        <v>0.062</v>
       </c>
       <c r="W30" t="n">
-        <v>0.5</v>
+        <v>0.156</v>
       </c>
       <c r="X30" t="n">
-        <v>0.269</v>
+        <v>0.094</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.308</v>
+        <v>0.781</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.654</v>
+        <v>1.281</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.87</v>
+        <v>0.61</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.308</v>
+        <v>0.219</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.885</v>
+        <v>0.375</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.348</v>
+        <v>0.583</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.423</v>
+        <v>0.094</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.808</v>
+        <v>0.219</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.507</v>
+        <v>0.429</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.308</v>
+        <v>0.062</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.615</v>
+        <v>0.188</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.692</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AL30" t="n">
-        <v>4</v>
+        <v>1.844</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.423</v>
+        <v>0.441</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>23:37</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>11.222</v>
+        <v>4.626</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.597</v>
+        <v>0.606</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.63</v>
+        <v>0.616</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.1</v>
+        <v>0.966</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.127</v>
+        <v>0.216</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.195</v>
+        <v>0.101</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.351</v>
+        <v>1.781</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#2 J. MARCOS (Per Game)</t>
+          <t>#3 M. CALE (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C31" t="n">
-        <v>3.821</v>
+        <v>6.962</v>
       </c>
       <c r="D31" t="n">
-        <v>0.607</v>
+        <v>1.615</v>
       </c>
       <c r="E31" t="n">
-        <v>1.214</v>
+        <v>2.115</v>
       </c>
       <c r="F31" t="n">
-        <v>0.786</v>
+        <v>1.038</v>
       </c>
       <c r="G31" t="n">
-        <v>1.964</v>
+        <v>2.692</v>
       </c>
       <c r="H31" t="n">
-        <v>0.25</v>
+        <v>0.615</v>
       </c>
       <c r="I31" t="n">
-        <v>0.357</v>
+        <v>0.846</v>
       </c>
       <c r="J31" t="n">
-        <v>1.786</v>
+        <v>0.615</v>
       </c>
       <c r="K31" t="n">
-        <v>0.964</v>
+        <v>1.423</v>
       </c>
       <c r="L31" t="n">
-        <v>0.179</v>
+        <v>0.538</v>
       </c>
       <c r="M31" t="n">
-        <v>0.607</v>
+        <v>0.769</v>
       </c>
       <c r="N31" t="n">
-        <v>0.321</v>
+        <v>0.115</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.107</v>
+        <v>0.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.107</v>
+        <v>0.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.036</v>
+        <v>2.231</v>
       </c>
       <c r="S31" t="n">
-        <v>0.75</v>
+        <v>0.962</v>
       </c>
       <c r="T31" t="n">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="U31" t="n">
-        <v>0.393</v>
+        <v>0.846</v>
       </c>
       <c r="V31" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="W31" t="n">
-        <v>0.179</v>
+        <v>0.385</v>
       </c>
       <c r="X31" t="n">
-        <v>0.107</v>
+        <v>0.192</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.536</v>
+        <v>1.885</v>
       </c>
       <c r="Z31" t="n">
-        <v>1</v>
+        <v>2.154</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.536</v>
+        <v>0.875</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.214</v>
+        <v>0.192</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.393</v>
+        <v>0.385</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.107</v>
+        <v>0.154</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.179</v>
+        <v>0.423</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.6</v>
+        <v>0.364</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.214</v>
+        <v>1.192</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.333</v>
+        <v>0.516</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.714</v>
+        <v>0.423</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.408</v>
+        <v>0.282</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>4.443</v>
+        <v>5.68</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.573</v>
+        <v>0.672</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.86</v>
+        <v>1.226</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.249</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.079</v>
+        <v>0.128</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.613</v>
+        <v>1.231</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.172</v>
+        <v>0.135</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.019</v>
+        <v>0.035</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.095</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.058</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#3 M. CALE (Per Game)</t>
+          <t>#5 M. NORRIS (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C32" t="n">
-        <v>7.045</v>
+        <v>7.222</v>
       </c>
       <c r="D32" t="n">
-        <v>1.727</v>
+        <v>1.333</v>
       </c>
       <c r="E32" t="n">
-        <v>2.273</v>
+        <v>2.056</v>
       </c>
       <c r="F32" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.278</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.222</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="T32" t="n">
+        <v>156</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.722</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.773</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.6820000000000001</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.182</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>140</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.273</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.227</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0.409</v>
-      </c>
       <c r="AL32" t="n">
-        <v>1.545</v>
+        <v>2.389</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.265</v>
+        <v>0.419</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>5.905</v>
+        <v>6.149</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.64</v>
+        <v>0.609</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.652</v>
+        <v>0.615</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.193</v>
+        <v>1.175</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.117</v>
+        <v>0.135</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.364</v>
+        <v>1.4</v>
       </c>
       <c r="AV32" t="n">
         <v>0.139</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.041</v>
+        <v>0.031</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.082</v>
+        <v>0.184</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.023</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#5 M. NORRIS (Per Game)</t>
+          <t>#6 J. VESELY (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C33" t="n">
-        <v>8.356999999999999</v>
+        <v>6.625</v>
       </c>
       <c r="D33" t="n">
-        <v>1.643</v>
+        <v>2.375</v>
       </c>
       <c r="E33" t="n">
-        <v>2.357</v>
+        <v>3.958</v>
       </c>
       <c r="F33" t="n">
-        <v>1.5</v>
+        <v>0.333</v>
       </c>
       <c r="G33" t="n">
-        <v>3.571</v>
+        <v>0.708</v>
       </c>
       <c r="H33" t="n">
-        <v>0.571</v>
+        <v>0.875</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="J33" t="n">
-        <v>0.286</v>
+        <v>1.083</v>
       </c>
       <c r="K33" t="n">
-        <v>3.571</v>
+        <v>1.708</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5</v>
+        <v>0.583</v>
       </c>
       <c r="M33" t="n">
-        <v>0.857</v>
+        <v>0.708</v>
       </c>
       <c r="N33" t="n">
-        <v>0.571</v>
+        <v>0.375</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.214</v>
+        <v>0.292</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.214</v>
+        <v>0.292</v>
       </c>
       <c r="R33" t="n">
-        <v>1.643</v>
+        <v>1.833</v>
       </c>
       <c r="S33" t="n">
-        <v>0.786</v>
+        <v>1.292</v>
       </c>
       <c r="T33" t="n">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="U33" t="n">
-        <v>1.643</v>
+        <v>0.75</v>
       </c>
       <c r="V33" t="n">
-        <v>1.286</v>
+        <v>0.25</v>
       </c>
       <c r="W33" t="n">
-        <v>0.571</v>
+        <v>0.25</v>
       </c>
       <c r="X33" t="n">
-        <v>0.214</v>
+        <v>0.125</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.786</v>
+        <v>1.667</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.357</v>
+        <v>2.042</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.758</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.357</v>
+        <v>0.667</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.643</v>
+        <v>1.083</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.556</v>
+        <v>0.615</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.917</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.357</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.2</v>
+        <v>0.458</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.143</v>
+        <v>0.333</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.429</v>
+        <v>0.708</v>
       </c>
       <c r="AM33" t="n">
         <v>0.471</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>22:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.583</v>
+        <v>5.472</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.657</v>
+        <v>0.616</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.656</v>
+        <v>0.639</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.27</v>
+        <v>1.211</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.033</v>
+        <v>0.053</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.096</v>
+        <v>0.188</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.333</v>
+        <v>3.714</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.143</v>
+        <v>0.174</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.029</v>
+        <v>0.051</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.198</v>
+        <v>0.138</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.01</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#6 J. VESELY (Per Game)</t>
+          <t>#8 D. BRIZUELA (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C34" t="n">
-        <v>6.625</v>
+        <v>8.632999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>2.375</v>
+        <v>1.5</v>
       </c>
       <c r="E34" t="n">
-        <v>3.958</v>
+        <v>2.633</v>
       </c>
       <c r="F34" t="n">
-        <v>0.333</v>
+        <v>1.6</v>
       </c>
       <c r="G34" t="n">
-        <v>0.708</v>
+        <v>4.2</v>
       </c>
       <c r="H34" t="n">
-        <v>0.875</v>
+        <v>0.833</v>
       </c>
       <c r="I34" t="n">
-        <v>1.167</v>
+        <v>1.033</v>
       </c>
       <c r="J34" t="n">
-        <v>1.083</v>
+        <v>1.633</v>
       </c>
       <c r="K34" t="n">
-        <v>1.708</v>
+        <v>0.9</v>
       </c>
       <c r="L34" t="n">
-        <v>0.583</v>
+        <v>0.2</v>
       </c>
       <c r="M34" t="n">
-        <v>0.708</v>
+        <v>0.533</v>
       </c>
       <c r="N34" t="n">
-        <v>0.375</v>
+        <v>0.133</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.292</v>
+        <v>0.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.292</v>
+        <v>0.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.833</v>
+        <v>1.867</v>
       </c>
       <c r="S34" t="n">
-        <v>1.292</v>
+        <v>1.467</v>
       </c>
       <c r="T34" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="U34" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="V34" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="W34" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="X34" t="n">
-        <v>0.125</v>
+        <v>0.367</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.667</v>
+        <v>1.233</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.042</v>
+        <v>1.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.771</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.083</v>
+        <v>1.267</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.615</v>
+        <v>0.553</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.917</v>
+        <v>0.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.458</v>
+        <v>0.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>0.767</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.333</v>
+        <v>1.367</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.708</v>
+        <v>3.433</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.471</v>
+        <v>0.398</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>5.472</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.616</v>
+        <v>0.571</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.639</v>
+        <v>0.592</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.211</v>
+        <v>1.054</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.053</v>
+        <v>0.11</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.188</v>
+        <v>0.122</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.714</v>
+        <v>1.815</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.175</v>
+        <v>0.249</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.05</v>
+        <v>0.017</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.14</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.037</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#8 D. BRIZUELA (Per Game)</t>
+          <t>#13 T. SATORANSKY (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C35" t="n">
-        <v>8.769</v>
+        <v>6.478</v>
       </c>
       <c r="D35" t="n">
-        <v>1.385</v>
+        <v>1.348</v>
       </c>
       <c r="E35" t="n">
-        <v>2.615</v>
+        <v>2.652</v>
       </c>
       <c r="F35" t="n">
-        <v>1.731</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>4.308</v>
+        <v>2.522</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.783</v>
       </c>
       <c r="I35" t="n">
-        <v>1.038</v>
+        <v>1.174</v>
       </c>
       <c r="J35" t="n">
-        <v>1.462</v>
+        <v>3.913</v>
       </c>
       <c r="K35" t="n">
-        <v>0.962</v>
+        <v>2.043</v>
       </c>
       <c r="L35" t="n">
-        <v>0.231</v>
+        <v>0.478</v>
       </c>
       <c r="M35" t="n">
-        <v>0.538</v>
+        <v>0.696</v>
       </c>
       <c r="N35" t="n">
-        <v>0.154</v>
+        <v>0.13</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.846</v>
+        <v>1.478</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.846</v>
+        <v>1.478</v>
       </c>
       <c r="R35" t="n">
-        <v>1.885</v>
+        <v>1.826</v>
       </c>
       <c r="S35" t="n">
-        <v>1.538</v>
+        <v>2.087</v>
       </c>
       <c r="T35" t="n">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="U35" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.957</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
         <v>1</v>
       </c>
-      <c r="V35" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.154</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.577</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.346</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AL35" t="n">
-        <v>3.577</v>
+        <v>2.348</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.419</v>
+        <v>0.426</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>8.226000000000001</v>
+        <v>7.169</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.575</v>
+        <v>0.55</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.594</v>
+        <v>0.569</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.066</v>
+        <v>0.904</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.103</v>
+        <v>0.206</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.117</v>
+        <v>0.151</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.727</v>
+        <v>2.647</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.254</v>
+        <v>0.153</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.019</v>
+        <v>0.028</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.076</v>
+        <v>0.111</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.05</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#13 T. SATORANSKY (Per Game)</t>
+          <t>#14 W. HERNANGÓMEZ (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>6.478</v>
+        <v>8.75</v>
       </c>
       <c r="D36" t="n">
-        <v>1.348</v>
+        <v>3.188</v>
       </c>
       <c r="E36" t="n">
-        <v>2.652</v>
+        <v>4.688</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2.522</v>
+        <v>0.062</v>
       </c>
       <c r="H36" t="n">
-        <v>0.783</v>
+        <v>2.375</v>
       </c>
       <c r="I36" t="n">
-        <v>1.174</v>
+        <v>3.375</v>
       </c>
       <c r="J36" t="n">
-        <v>3.913</v>
+        <v>0.594</v>
       </c>
       <c r="K36" t="n">
-        <v>2.043</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>0.478</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>0.696</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>0.13</v>
+        <v>0.844</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.478</v>
+        <v>0.969</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.478</v>
+        <v>0.969</v>
       </c>
       <c r="R36" t="n">
-        <v>1.826</v>
+        <v>1.719</v>
       </c>
       <c r="S36" t="n">
-        <v>2.087</v>
+        <v>3.281</v>
       </c>
       <c r="T36" t="n">
-        <v>214</v>
+        <v>417</v>
       </c>
       <c r="U36" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="V36" t="n">
-        <v>0.261</v>
+        <v>1.406</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.348</v>
+        <v>4.656</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.957</v>
+        <v>6.031</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.772</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.391</v>
+        <v>0.656</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.826</v>
+        <v>1.375</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.474</v>
+        <v>0.477</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.391</v>
+        <v>0.25</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.043</v>
+        <v>0.656</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.375</v>
+        <v>0.381</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.348</v>
+        <v>0.062</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.426</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>7.169</v>
+        <v>7.204</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.55</v>
+        <v>0.671</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.569</v>
+        <v>0.702</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.904</v>
+        <v>1.215</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.206</v>
+        <v>0.134</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.151</v>
+        <v>0.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.647</v>
+        <v>0.613</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.154</v>
+        <v>0.209</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.028</v>
+        <v>0.099</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.112</v>
+        <v>0.221</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.13</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#14 W. HERNANGÓMEZ (Per Game)</t>
+          <t>#17 J. NÚÑEZ (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>8.393000000000001</v>
+        <v>5.429</v>
       </c>
       <c r="D37" t="n">
-        <v>3.143</v>
+        <v>1.714</v>
       </c>
       <c r="E37" t="n">
-        <v>4.643</v>
+        <v>2.857</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="G37" t="n">
-        <v>0.036</v>
+        <v>1.429</v>
       </c>
       <c r="H37" t="n">
-        <v>2.107</v>
+        <v>1.143</v>
       </c>
       <c r="I37" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="J37" t="n">
         <v>3</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="T37" t="n">
+        <v>56</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.286</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.286</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AD37" t="n">
         <v>0.5</v>
       </c>
-      <c r="K37" t="n">
-        <v>2.714</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="AE37" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="AP37" t="n">
         <v>0.5</v>
       </c>
-      <c r="N37" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.643</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.214</v>
-      </c>
-      <c r="T37" t="n">
-        <v>345</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.393</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>4.393</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>5.571</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.788</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>7.034</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.672</v>
-      </c>
       <c r="AQ37" t="n">
-        <v>0.7</v>
+        <v>0.532</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.193</v>
+        <v>0.78</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.147</v>
+        <v>0.267</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.45</v>
+        <v>0.267</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.483</v>
+        <v>1.615</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.207</v>
+        <v>0.194</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.099</v>
+        <v>0.022</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.204</v>
+        <v>0.181</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.017</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#17 J. NÚÑEZ (Per Game)</t>
+          <t>#19 Y. FALL (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4.938</v>
       </c>
       <c r="D38" t="n">
-        <v>1.333</v>
+        <v>2.156</v>
       </c>
       <c r="E38" t="n">
-        <v>2.333</v>
+        <v>3.031</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.333</v>
+        <v>0.625</v>
       </c>
       <c r="I38" t="n">
-        <v>0.667</v>
+        <v>0.781</v>
       </c>
       <c r="J38" t="n">
-        <v>2.333</v>
+        <v>0.188</v>
       </c>
       <c r="K38" t="n">
-        <v>1.333</v>
+        <v>1.531</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="M38" t="n">
-        <v>0.333</v>
+        <v>0.094</v>
       </c>
       <c r="N38" t="n">
-        <v>0.333</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.667</v>
+        <v>0.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.667</v>
+        <v>0.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.667</v>
+        <v>1.094</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="T38" t="n">
-        <v>8</v>
+        <v>221</v>
       </c>
       <c r="U38" t="n">
-        <v>1.333</v>
+        <v>0.438</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.656</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>2.156</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.333</v>
+        <v>2.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.75</v>
+        <v>0.784</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.333</v>
+        <v>0.406</v>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>0.656</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.333</v>
+        <v>0.619</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.333</v>
+        <v>0.219</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.667</v>
+        <v>0.406</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.5</v>
+        <v>0.538</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -6195,1174 +6195,1174 @@
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
         <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>5.293</v>
+        <v>3.875</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.4</v>
+        <v>0.711</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.414</v>
+        <v>0.731</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.5669999999999999</v>
+        <v>1.274</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.315</v>
+        <v>0.129</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.1</v>
+        <v>0.206</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.4</v>
+        <v>0.375</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.186</v>
+        <v>0.224</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>0.221</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.12</v>
+        <v>0.224</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.075</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#19 Y. FALL (Per Game)</t>
+          <t>#20 N. LAPROVITTOLA (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C39" t="n">
-        <v>3.929</v>
+        <v>11.308</v>
       </c>
       <c r="D39" t="n">
-        <v>1.714</v>
+        <v>2.154</v>
       </c>
       <c r="E39" t="n">
-        <v>2.464</v>
+        <v>3.308</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1.846</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4.462</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5</v>
+        <v>1.462</v>
       </c>
       <c r="I39" t="n">
-        <v>0.643</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>0.143</v>
+        <v>3.769</v>
       </c>
       <c r="K39" t="n">
-        <v>1.286</v>
+        <v>1.462</v>
       </c>
       <c r="L39" t="n">
-        <v>1.214</v>
+        <v>0.385</v>
       </c>
       <c r="M39" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="N39" t="n">
-        <v>0.321</v>
+        <v>0.308</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.357</v>
+        <v>1.692</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.357</v>
+        <v>1.692</v>
       </c>
       <c r="R39" t="n">
-        <v>0.929</v>
+        <v>2.385</v>
       </c>
       <c r="S39" t="n">
-        <v>0.714</v>
+        <v>2.462</v>
       </c>
       <c r="T39" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="U39" t="n">
-        <v>0.5</v>
+        <v>1.308</v>
       </c>
       <c r="V39" t="n">
-        <v>1.179</v>
+        <v>0.846</v>
       </c>
       <c r="W39" t="n">
-        <v>0.107</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="X39" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.462</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.679</v>
+        <v>2.538</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.25</v>
+        <v>3.538</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.746</v>
+        <v>0.717</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.357</v>
+        <v>0.923</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.5</v>
+        <v>1.308</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.714</v>
+        <v>0.706</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.179</v>
+        <v>0.154</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.357</v>
+        <v>0.462</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>3.104</v>
+        <v>10.342</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.696</v>
+        <v>0.634</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.715</v>
+        <v>0.654</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.266</v>
+        <v>1.093</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.115</v>
+        <v>0.164</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.203</v>
+        <v>0.188</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.4</v>
+        <v>2.227</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.224</v>
+        <v>0.251</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.237</v>
+        <v>0.025</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.238</v>
+        <v>0.09</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.005</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#20 N. LAPROVITTOLA (Per Game)</t>
+          <t>#21 W. CLYBURN (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C40" t="n">
-        <v>11.308</v>
+        <v>12.4</v>
       </c>
       <c r="D40" t="n">
-        <v>2.154</v>
+        <v>2.25</v>
       </c>
       <c r="E40" t="n">
-        <v>3.308</v>
+        <v>4.25</v>
       </c>
       <c r="F40" t="n">
-        <v>1.846</v>
+        <v>1.85</v>
       </c>
       <c r="G40" t="n">
-        <v>4.462</v>
+        <v>4.5</v>
       </c>
       <c r="H40" t="n">
-        <v>1.462</v>
+        <v>2.35</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="J40" t="n">
-        <v>3.769</v>
+        <v>1.6</v>
       </c>
       <c r="K40" t="n">
-        <v>1.462</v>
+        <v>3.1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.385</v>
+        <v>0.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0.615</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0.308</v>
+        <v>0.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.692</v>
+        <v>1.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.692</v>
+        <v>1.25</v>
       </c>
       <c r="R40" t="n">
-        <v>2.385</v>
+        <v>1.75</v>
       </c>
       <c r="S40" t="n">
-        <v>2.462</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
-        <v>155</v>
+        <v>265</v>
       </c>
       <c r="U40" t="n">
-        <v>1.308</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>0.846</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="X40" t="n">
-        <v>0.462</v>
+        <v>0.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.538</v>
+        <v>3.7</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.538</v>
+        <v>4.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.717</v>
+        <v>0.755</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.923</v>
+        <v>0.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.308</v>
+        <v>1.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.706</v>
+        <v>0.542</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.154</v>
+        <v>0.25</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.462</v>
+        <v>1.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.333</v>
+        <v>0.192</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.385</v>
+        <v>0.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.462</v>
+        <v>0.95</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.833</v>
+        <v>0.526</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.462</v>
+        <v>1.35</v>
       </c>
       <c r="AL40" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.365</v>
+        <v>0.38</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>23:38</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>10.342</v>
+        <v>11.386</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.634</v>
+        <v>0.574</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.654</v>
+        <v>0.612</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.093</v>
+        <v>1.089</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.164</v>
+        <v>0.11</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.188</v>
+        <v>0.269</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.227</v>
+        <v>1.28</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.252</v>
+        <v>0.233</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.025</v>
+        <v>0.033</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.091</v>
+        <v>0.16</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.133</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#21 W. CLYBURN (Per Game)</t>
+          <t>#23 T. SHENGELIA (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C41" t="n">
-        <v>12.4</v>
+        <v>10.25</v>
       </c>
       <c r="D41" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="E41" t="n">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="F41" t="n">
-        <v>1.85</v>
+        <v>0.179</v>
       </c>
       <c r="G41" t="n">
-        <v>4.5</v>
+        <v>1.536</v>
       </c>
       <c r="H41" t="n">
-        <v>2.35</v>
+        <v>2.714</v>
       </c>
       <c r="I41" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
-        <v>1.6</v>
+        <v>1.857</v>
       </c>
       <c r="K41" t="n">
-        <v>3.1</v>
+        <v>2.571</v>
       </c>
       <c r="L41" t="n">
-        <v>0.6</v>
+        <v>0.964</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0.607</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2</v>
+        <v>0.821</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.75</v>
+        <v>2.143</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>4.179</v>
       </c>
       <c r="T41" t="n">
-        <v>265</v>
+        <v>377</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0.964</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.179</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2</v>
+        <v>0.464</v>
       </c>
       <c r="X41" t="n">
-        <v>0.75</v>
+        <v>0.321</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.7</v>
+        <v>5.036</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.9</v>
+        <v>6.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.755</v>
+        <v>0.746</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.65</v>
+        <v>0.857</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.2</v>
+        <v>1.607</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.542</v>
+        <v>0.533</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.25</v>
+        <v>0.321</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.3</v>
+        <v>0.643</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.192</v>
+        <v>0.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.5</v>
+        <v>0.036</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.95</v>
+        <v>0.214</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.526</v>
+        <v>0.167</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.35</v>
+        <v>0.143</v>
       </c>
       <c r="AL41" t="n">
-        <v>3.55</v>
+        <v>1.321</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.38</v>
+        <v>0.108</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>23:38</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>11.386</v>
+        <v>10.076</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.574</v>
+        <v>0.536</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.612</v>
+        <v>0.598</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.089</v>
+        <v>1.017</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.11</v>
+        <v>0.149</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.269</v>
+        <v>0.386</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.28</v>
+        <v>1.238</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.033</v>
+        <v>0.062</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.163</v>
+        <v>0.153</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.057</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#23 T. SHENGELIA (Per Game)</t>
+          <t>#41 S. KEITA (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C42" t="n">
-        <v>10.083</v>
+        <v>0.533</v>
       </c>
       <c r="D42" t="n">
-        <v>3.292</v>
+        <v>0.2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.125</v>
+        <v>0.6</v>
       </c>
       <c r="F42" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1.542</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>0.133</v>
       </c>
       <c r="I42" t="n">
-        <v>3.833</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
-        <v>1.792</v>
+        <v>0.067</v>
       </c>
       <c r="K42" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="L42" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="M42" t="n">
-        <v>0.542</v>
+        <v>0.133</v>
       </c>
       <c r="N42" t="n">
-        <v>0.792</v>
+        <v>0.333</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.417</v>
+        <v>0.267</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.417</v>
+        <v>0.267</v>
       </c>
       <c r="R42" t="n">
-        <v>2.292</v>
+        <v>0.8</v>
       </c>
       <c r="S42" t="n">
-        <v>4.167</v>
+        <v>0.267</v>
       </c>
       <c r="T42" t="n">
-        <v>309</v>
+        <v>6</v>
       </c>
       <c r="U42" t="n">
-        <v>1.042</v>
+        <v>0.133</v>
       </c>
       <c r="V42" t="n">
-        <v>1.208</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0.458</v>
+        <v>0.133</v>
       </c>
       <c r="X42" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="AP42" t="n">
         <v>0.333</v>
       </c>
-      <c r="Y42" t="n">
-        <v>5.167</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>6.875</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="AI42" t="n">
+      <c r="AQ42" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AU42" t="n">
         <v>0.25</v>
       </c>
-      <c r="AJ42" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.292</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="AO42" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.032</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>1.265</v>
-      </c>
       <c r="AV42" t="n">
-        <v>0.234</v>
+        <v>0.153</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.049</v>
+        <v>0.16</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.153</v>
+        <v>0.149</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.062</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#41 S. KEITA (Per Game)</t>
+          <t>#43 N. KUSTURICA (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>11</v>
       </c>
       <c r="C43" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>0.273</v>
       </c>
-      <c r="D43" t="n">
+      <c r="Q43" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="T43" t="n">
+        <v>26</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="X43" t="n">
         <v>0.091</v>
       </c>
-      <c r="E43" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
+      <c r="Y43" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AB43" t="n">
         <v>0.091</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="T43" t="n">
-        <v>4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0.091</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.182</v>
+        <v>0.364</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="AJ43" t="n">
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>03:56</t>
+          <t>04:36</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>0.978</v>
+        <v>2.058</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.143</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.171</v>
+        <v>0.535</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.279</v>
+        <v>0.928</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.186</v>
+        <v>0.133</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.143</v>
+        <v>0.118</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.12</v>
+        <v>0.216</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.181</v>
+        <v>0.13</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.172</v>
+        <v>0.242</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#43 N. KUSTURICA (Per Game)</t>
+          <t>#44 J. PARRA (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C44" t="n">
-        <v>1.909</v>
+        <v>8.452</v>
       </c>
       <c r="D44" t="n">
-        <v>0.727</v>
+        <v>2.226</v>
       </c>
       <c r="E44" t="n">
-        <v>1.091</v>
+        <v>3.452</v>
       </c>
       <c r="F44" t="n">
-        <v>0.091</v>
+        <v>0.839</v>
       </c>
       <c r="G44" t="n">
-        <v>0.455</v>
+        <v>2.387</v>
       </c>
       <c r="H44" t="n">
-        <v>0.182</v>
+        <v>1.484</v>
       </c>
       <c r="I44" t="n">
-        <v>0.545</v>
+        <v>1.968</v>
       </c>
       <c r="J44" t="n">
-        <v>0.182</v>
+        <v>1.355</v>
       </c>
       <c r="K44" t="n">
-        <v>0.909</v>
+        <v>3.452</v>
       </c>
       <c r="L44" t="n">
-        <v>0.455</v>
+        <v>1.194</v>
       </c>
       <c r="M44" t="n">
-        <v>0.364</v>
+        <v>0.871</v>
       </c>
       <c r="N44" t="n">
-        <v>0.182</v>
+        <v>0.419</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.273</v>
+        <v>0.806</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.273</v>
+        <v>0.806</v>
       </c>
       <c r="R44" t="n">
-        <v>0.727</v>
+        <v>1.484</v>
       </c>
       <c r="S44" t="n">
-        <v>0.455</v>
+        <v>1.935</v>
       </c>
       <c r="T44" t="n">
-        <v>26</v>
+        <v>376</v>
       </c>
       <c r="U44" t="n">
-        <v>0.455</v>
+        <v>0.645</v>
       </c>
       <c r="V44" t="n">
-        <v>0.364</v>
+        <v>1.161</v>
       </c>
       <c r="W44" t="n">
-        <v>0.182</v>
+        <v>0.548</v>
       </c>
       <c r="X44" t="n">
-        <v>0.091</v>
+        <v>0.387</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.727</v>
+        <v>2.742</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.182</v>
+        <v>3.516</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.615</v>
+        <v>0.78</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.091</v>
+        <v>0.645</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.091</v>
+        <v>1.161</v>
       </c>
       <c r="AD44" t="n">
-        <v>1</v>
+        <v>0.556</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.091</v>
+        <v>0.323</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.364</v>
+        <v>0.742</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.25</v>
+        <v>0.435</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.091</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.091</v>
+        <v>0.29</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.364</v>
+        <v>1.452</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>04:36</t>
+          <t>22:53</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>2.058</v>
+        <v>7.511</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.597</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.535</v>
+        <v>0.63</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.928</v>
+        <v>1.125</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.133</v>
+        <v>0.107</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.118</v>
+        <v>0.254</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.667</v>
+        <v>1.68</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.217</v>
+        <v>0.158</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.129</v>
+        <v>0.068</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.245</v>
+        <v>0.185</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.006</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#44 J. PARRA (Per Game)</t>
+          <t>#47 D. GONZÁLEZ (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>8.519</v>
+        <v>0.3</v>
       </c>
       <c r="D45" t="n">
-        <v>2.148</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.926</v>
+        <v>0.1</v>
       </c>
       <c r="G45" t="n">
-        <v>2.481</v>
+        <v>0.3</v>
       </c>
       <c r="H45" t="n">
-        <v>1.444</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1.926</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1.37</v>
+        <v>0.1</v>
       </c>
       <c r="K45" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1.296</v>
+        <v>0.1</v>
       </c>
       <c r="M45" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0.481</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="R45" t="n">
-        <v>1.556</v>
+        <v>0.2</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="T45" t="n">
-        <v>332</v>
+        <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>0.593</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.111</v>
+        <v>0.3</v>
       </c>
       <c r="W45" t="n">
-        <v>0.481</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.407</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.148</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.581</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.704</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.593</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.963</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM45" t="n">
         <v>0.333</v>
       </c>
-      <c r="AL45" t="n">
-        <v>1.519</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0.22</v>
-      </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>02:02</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>7.477</v>
+        <v>0.6</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.608</v>
+        <v>0.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.639</v>
+        <v>0.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.139</v>
+        <v>0.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.109</v>
+        <v>0.5</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.682</v>
+        <v>0.333</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.158</v>
+        <v>0.141</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.074</v>
+        <v>0.064</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.047</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#47 D. GONZÁLEZ (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -7371,10 +7371,10 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1.469</v>
       </c>
       <c r="L46" t="n">
-        <v>0.167</v>
+        <v>1.062</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7401,16 +7401,16 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.333</v>
+        <v>0.844</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.333</v>
+        <v>0.156</v>
       </c>
       <c r="S46" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -7419,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -7464,33 +7464,33 @@
         <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>02:06</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
         <v>0</v>
@@ -7499,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
@@ -7514,157 +7514,157 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>89.65600000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>22.938</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>37.125</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9.875</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>25.625</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>14.156</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>19.188</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>16.406</v>
       </c>
       <c r="K47" t="n">
-        <v>1.571</v>
+        <v>24.406</v>
       </c>
       <c r="L47" t="n">
-        <v>0.893</v>
+        <v>8.75</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>7.438</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.812</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.929</v>
+        <v>11.656</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>10.812</v>
       </c>
       <c r="R47" t="n">
-        <v>0.179</v>
+        <v>20.5</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>21.562</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3389</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>9.625</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>9.218999999999999</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4.594</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.688</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>35.438</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>5.719</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>10.656</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.537</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>4.375</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>10.219</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>5.031</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.447</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>7.625</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>20.594</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>0</v>
+        <v>82.849</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>0.602</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.082</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>1.408</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -7673,477 +7673,159 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>81.812</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>20.156</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>35.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>24.969</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>15.438</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>19.844</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>16.375</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>21.719</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>8.281000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>6.125</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.781</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>12.906</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>12.062</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>21.656</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>20.281</v>
       </c>
       <c r="T48" t="n">
-        <v>38</v>
+        <v>2841</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>9.875</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7.656</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4.125</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.469</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>27.812</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>36.25</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>0.767</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>4.625</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>9.938000000000001</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>3.156</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>9.156000000000001</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>2.062</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>5.938</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>6.625</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>19.031</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>0.348</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>0.929</v>
+        <v>82.10599999999999</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>0.996</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>1.269</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>28</v>
-      </c>
-      <c r="C49" t="n">
-        <v>88.714</v>
-      </c>
-      <c r="D49" t="n">
-        <v>22.179</v>
-      </c>
-      <c r="E49" t="n">
-        <v>36.357</v>
-      </c>
-      <c r="F49" t="n">
-        <v>10.179</v>
-      </c>
-      <c r="G49" t="n">
-        <v>26.286</v>
-      </c>
-      <c r="H49" t="n">
-        <v>13.821</v>
-      </c>
-      <c r="I49" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="J49" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K49" t="n">
-        <v>23.929</v>
-      </c>
-      <c r="L49" t="n">
-        <v>8.536</v>
-      </c>
-      <c r="M49" t="n">
-        <v>7.393</v>
-      </c>
-      <c r="N49" t="n">
-        <v>4.643</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>11.607</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>10.679</v>
-      </c>
-      <c r="R49" t="n">
-        <v>20.857</v>
-      </c>
-      <c r="S49" t="n">
-        <v>21.607</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2902</v>
-      </c>
-      <c r="U49" t="n">
-        <v>9.536</v>
-      </c>
-      <c r="V49" t="n">
-        <v>8.821</v>
-      </c>
-      <c r="W49" t="n">
-        <v>4.536</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.643</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>26.071</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>34.286</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>5.714</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>10.786</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>4.214</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>10.036</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>2.357</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>5.214</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>7.821</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>21.071</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO49" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0.626</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.075</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>1.422</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>28</v>
-      </c>
-      <c r="C50" t="n">
-        <v>81.357</v>
-      </c>
-      <c r="D50" t="n">
-        <v>20.607</v>
-      </c>
-      <c r="E50" t="n">
-        <v>35.857</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8.179</v>
-      </c>
-      <c r="G50" t="n">
-        <v>24.357</v>
-      </c>
-      <c r="H50" t="n">
-        <v>15.607</v>
-      </c>
-      <c r="I50" t="n">
-        <v>20.036</v>
-      </c>
-      <c r="J50" t="n">
-        <v>16.786</v>
-      </c>
-      <c r="K50" t="n">
-        <v>22</v>
-      </c>
-      <c r="L50" t="n">
-        <v>8.321</v>
-      </c>
-      <c r="M50" t="n">
-        <v>6.107</v>
-      </c>
-      <c r="N50" t="n">
-        <v>4.643</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>12.929</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>12.071</v>
-      </c>
-      <c r="R50" t="n">
-        <v>21.679</v>
-      </c>
-      <c r="S50" t="n">
-        <v>20.607</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2502</v>
-      </c>
-      <c r="U50" t="n">
-        <v>9.786</v>
-      </c>
-      <c r="V50" t="n">
-        <v>7.679</v>
-      </c>
-      <c r="W50" t="n">
-        <v>4.036</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.464</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>28.321</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>36.607</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>4.857</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>9.964</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>3.036</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>9.321</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>5.893</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>6.179</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>18.464</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO50" t="n">
-        <v>81.959</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1.298</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="AY50" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Barça.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Barça.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2371.16</v>
+        <v>2530.08</v>
       </c>
       <c r="C2" t="n">
-        <v>2366.78</v>
+        <v>2527.3</v>
       </c>
       <c r="D2" t="n">
-        <v>121.2195472329494</v>
+        <v>120.5238792387133</v>
       </c>
       <c r="E2" t="n">
-        <v>110.6144212812344</v>
+        <v>111.3836901040636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.601593625498008</v>
+        <v>0.5967365967365967</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1406931305541725</v>
+        <v>0.1405327533120533</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2871794871794872</v>
+        <v>0.2867996201329535</v>
       </c>
       <c r="I2" t="n">
-        <v>0.225597609561753</v>
+        <v>0.2265734265734266</v>
       </c>
       <c r="J2" t="n">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="K2" t="n">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="L2" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="M2" t="n">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="N2" t="n">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="O2" t="n">
-        <v>1134</v>
+        <v>1199</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5647410358565738</v>
+        <v>0.558974358974359</v>
       </c>
       <c r="Q2" t="n">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="R2" t="n">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1698207171314741</v>
+        <v>0.1766899766899767</v>
       </c>
       <c r="T2" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="U2" t="n">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1628486055776892</v>
+        <v>0.1655011655011655</v>
       </c>
       <c r="W2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="X2" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08017928286852589</v>
+        <v>0.08018648018648018</v>
       </c>
       <c r="Z2" t="n">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="AA2" t="n">
-        <v>659</v>
+        <v>697</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3281872509960159</v>
+        <v>0.324941724941725</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7656380316930775</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5366568914956011</v>
+        <v>0.5329815303430079</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4281345565749236</v>
+        <v>0.4169014084507042</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4472049689440994</v>
+        <v>0.436046511627907</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.370257966616085</v>
+        <v>0.3687230989956958</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.523809523809524</v>
+        <v>1.531276063386155</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.8562691131498471</v>
+        <v>0.8338028169014085</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15609756097561</v>
+        <v>1.14614499424626</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7457627118644068</v>
+        <v>0.7539503386004515</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.053571428571429</v>
+        <v>1.072847682119205</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.709302325581395</v>
+        <v>1.734042553191489</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.407506702412869</v>
+        <v>1.384422110552764</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.383378016085791</v>
+        <v>5.389447236180905</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.79088471849866</v>
+        <v>6.773869346733668</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.09875000000001</v>
+        <v>74.41411764705883</v>
       </c>
       <c r="C3" t="n">
-        <v>73.96187499999999</v>
+        <v>74.33235294117647</v>
       </c>
       <c r="D3" t="n">
-        <v>121.2195472329494</v>
+        <v>120.5238792387133</v>
       </c>
       <c r="E3" t="n">
-        <v>110.6144212812344</v>
+        <v>111.3836901040636</v>
       </c>
       <c r="F3" t="n">
-        <v>0.601593625498008</v>
+        <v>0.5967365967365967</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1406931305541725</v>
+        <v>0.1405327533120533</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2871794871794872</v>
+        <v>0.2867996201329535</v>
       </c>
       <c r="I3" t="n">
-        <v>0.225597609561753</v>
+        <v>0.2265734265734266</v>
       </c>
       <c r="J3" t="n">
-        <v>9.625</v>
+        <v>9.823529411764707</v>
       </c>
       <c r="K3" t="n">
-        <v>9.21875</v>
+        <v>9.529411764705882</v>
       </c>
       <c r="L3" t="n">
-        <v>4.59375</v>
+        <v>4.794117647058823</v>
       </c>
       <c r="M3" t="n">
-        <v>10.8125</v>
+        <v>10.91176470588235</v>
       </c>
       <c r="N3" t="n">
         <v>27</v>
       </c>
       <c r="O3" t="n">
-        <v>35.4375</v>
+        <v>35.26470588235294</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5647410358565738</v>
+        <v>0.558974358974359</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.71875</v>
+        <v>5.941176470588236</v>
       </c>
       <c r="R3" t="n">
-        <v>10.65625</v>
+        <v>11.14705882352941</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1698207171314741</v>
+        <v>0.1766899766899767</v>
       </c>
       <c r="T3" t="n">
-        <v>4.375</v>
+        <v>4.352941176470588</v>
       </c>
       <c r="U3" t="n">
-        <v>10.21875</v>
+        <v>10.44117647058824</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1628486055776892</v>
+        <v>0.1655011655011655</v>
       </c>
       <c r="W3" t="n">
-        <v>2.25</v>
+        <v>2.205882352941177</v>
       </c>
       <c r="X3" t="n">
-        <v>5.03125</v>
+        <v>5.058823529411764</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08017928286852589</v>
+        <v>0.08018648018648018</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.625</v>
+        <v>7.558823529411764</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.59375</v>
+        <v>20.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3281872509960159</v>
+        <v>0.3249417249417249</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7656380316930775</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5366568914956011</v>
+        <v>0.532981530343008</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4281345565749236</v>
+        <v>0.4169014084507042</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4472049689440994</v>
+        <v>0.436046511627907</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.370257966616085</v>
+        <v>0.3687230989956958</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.523809523809524</v>
+        <v>1.531276063386155</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8562691131498471</v>
+        <v>0.8338028169014083</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15609756097561</v>
+        <v>1.14614499424626</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7457627118644068</v>
+        <v>0.7539503386004516</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.053571428571429</v>
+        <v>1.072847682119205</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.709302325581395</v>
+        <v>1.734042553191489</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.407506702412869</v>
+        <v>1.384422110552764</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.383378016085791</v>
+        <v>5.389447236180906</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.79088471849866</v>
+        <v>6.773869346733669</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2362.4</v>
+        <v>2524.52</v>
       </c>
       <c r="C4" t="n">
-        <v>2366.78</v>
+        <v>2527.3</v>
       </c>
       <c r="D4" t="n">
-        <v>110.6144212812344</v>
+        <v>111.3836901040636</v>
       </c>
       <c r="E4" t="n">
-        <v>121.2195472329494</v>
+        <v>120.5238792387133</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5488372093023256</v>
+        <v>0.5519574673755437</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1571896171119738</v>
+        <v>0.1575099910400637</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2533460803059274</v>
+        <v>0.2578334825425246</v>
       </c>
       <c r="I4" t="n">
-        <v>0.255297157622739</v>
+        <v>0.2566457225712905</v>
       </c>
       <c r="J4" t="n">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="L4" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="M4" t="n">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="N4" t="n">
-        <v>890</v>
+        <v>952</v>
       </c>
       <c r="O4" t="n">
-        <v>1160</v>
+        <v>1237</v>
       </c>
       <c r="P4" t="n">
-        <v>0.599483204134367</v>
+        <v>0.597873368777187</v>
       </c>
       <c r="Q4" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="R4" t="n">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1643410852713178</v>
+        <v>0.1643305944900918</v>
       </c>
       <c r="T4" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="U4" t="n">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1514211886304909</v>
+        <v>0.1512808119864669</v>
       </c>
       <c r="W4" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="X4" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09819121447028424</v>
+        <v>0.09908168197196714</v>
       </c>
       <c r="Z4" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="AA4" t="n">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3147286821705426</v>
+        <v>0.3175447075882069</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7672413793103449</v>
+        <v>0.7696038803556993</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4654088050314465</v>
+        <v>0.4735294117647059</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3447098976109215</v>
+        <v>0.34185303514377</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3473684210526316</v>
+        <v>0.3560975609756097</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3481116584564861</v>
+        <v>0.3485540334855403</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.53448275862069</v>
+        <v>1.539207760711399</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.689419795221843</v>
+        <v>0.6837060702875399</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.043804755944931</v>
+        <v>1.051044083526682</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8471849865951743</v>
+        <v>0.8743718592964824</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.670886075949367</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.268765133171913</v>
+        <v>1.257336343115124</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.685230024213075</v>
+        <v>4.670428893905192</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.953995157384988</v>
+        <v>5.927765237020316</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.82499999999999</v>
+        <v>74.25058823529412</v>
       </c>
       <c r="C5" t="n">
-        <v>73.96187499999999</v>
+        <v>74.33235294117647</v>
       </c>
       <c r="D5" t="n">
-        <v>110.6144212812344</v>
+        <v>111.3836901040636</v>
       </c>
       <c r="E5" t="n">
-        <v>121.2195472329494</v>
+        <v>120.5238792387133</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5488372093023256</v>
+        <v>0.5519574673755439</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1571896171119738</v>
+        <v>0.1575099910400637</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2533460803059274</v>
+        <v>0.2578334825425246</v>
       </c>
       <c r="I5" t="n">
-        <v>0.255297157622739</v>
+        <v>0.2566457225712905</v>
       </c>
       <c r="J5" t="n">
-        <v>9.875</v>
+        <v>10.23529411764706</v>
       </c>
       <c r="K5" t="n">
-        <v>7.65625</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>4.125</v>
+        <v>4.235294117647059</v>
       </c>
       <c r="M5" t="n">
-        <v>12.0625</v>
+        <v>12.20588235294118</v>
       </c>
       <c r="N5" t="n">
-        <v>27.8125</v>
+        <v>28</v>
       </c>
       <c r="O5" t="n">
-        <v>36.25</v>
+        <v>36.38235294117647</v>
       </c>
       <c r="P5" t="n">
-        <v>0.599483204134367</v>
+        <v>0.5978733687771871</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.625</v>
+        <v>4.735294117647059</v>
       </c>
       <c r="R5" t="n">
-        <v>9.9375</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1643410852713178</v>
+        <v>0.1643305944900918</v>
       </c>
       <c r="T5" t="n">
-        <v>3.15625</v>
+        <v>3.147058823529412</v>
       </c>
       <c r="U5" t="n">
-        <v>9.15625</v>
+        <v>9.205882352941176</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1514211886304909</v>
+        <v>0.1512808119864669</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0625</v>
+        <v>2.147058823529412</v>
       </c>
       <c r="X5" t="n">
-        <v>5.9375</v>
+        <v>6.029411764705882</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09819121447028424</v>
+        <v>0.09908168197196714</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.625</v>
+        <v>6.735294117647059</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.03125</v>
+        <v>19.32352941176471</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3147286821705426</v>
+        <v>0.3175447075882069</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7672413793103449</v>
+        <v>0.7696038803556993</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4654088050314465</v>
+        <v>0.4735294117647059</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3447098976109215</v>
+        <v>0.34185303514377</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3473684210526316</v>
+        <v>0.3560975609756097</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3481116584564861</v>
+        <v>0.3485540334855403</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53448275862069</v>
+        <v>1.539207760711399</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.689419795221843</v>
+        <v>0.6837060702875399</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.043804755944931</v>
+        <v>1.051044083526682</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8471849865951743</v>
+        <v>0.8743718592964824</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.670886075949367</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.268765133171913</v>
+        <v>1.257336343115124</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.685230024213075</v>
+        <v>4.670428893905192</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.953995157384988</v>
+        <v>5.927765237020316</v>
       </c>
     </row>
     <row r="7">
@@ -1419,40 +1419,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>396</v>
+        <v>427</v>
       </c>
       <c r="D8" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H8" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J8" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
         <v>13</v>
@@ -1461,114 +1461,114 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R8" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="S8" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="T8" t="n">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="U8" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="V8" t="n">
         <v>24</v>
       </c>
       <c r="W8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="Z8" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AA8" t="n">
         <v>0.889</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AC8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.4</v>
+        <v>0.441</v>
       </c>
       <c r="AE8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF8" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.505</v>
+        <v>0.48</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.45</v>
+        <v>0.458</v>
       </c>
       <c r="AK8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AL8" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>707:50</t>
+          <t>763:00</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>351.28</v>
+        <v>380.8</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.612</v>
+        <v>0.606</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.644</v>
+        <v>0.64</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.127</v>
+        <v>1.121</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.125</v>
+        <v>0.123</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.189</v>
+        <v>0.198</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.25</v>
+        <v>1.255</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.24</v>
+        <v>0.241</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="9">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N9" t="n">
         <v>12</v>
@@ -1620,19 +1620,19 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>68</v>
+      </c>
+      <c r="S9" t="n">
         <v>32</v>
       </c>
-      <c r="Q9" t="n">
-        <v>32</v>
-      </c>
-      <c r="R9" t="n">
-        <v>63</v>
-      </c>
-      <c r="S9" t="n">
-        <v>26</v>
-      </c>
       <c r="T9" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="U9" t="n">
         <v>17</v>
@@ -1647,31 +1647,31 @@
         <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.61</v>
+        <v>0.614</v>
       </c>
       <c r="AB9" t="n">
         <v>7</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.583</v>
+        <v>0.467</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.429</v>
+        <v>0.3</v>
       </c>
       <c r="AH9" t="n">
         <v>2</v>
@@ -1683,51 +1683,51 @@
         <v>0.333</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.441</v>
+        <v>0.446</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>421:08</t>
+          <t>461:32</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>148.04</v>
+        <v>163.92</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.606</v>
+        <v>0.586</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.616</v>
+        <v>0.597</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.966</v>
+        <v>0.946</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.216</v>
+        <v>0.207</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.101</v>
+        <v>0.098</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.781</v>
+        <v>1.794</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.099</v>
+        <v>0.103</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="10">
@@ -1737,22 +1737,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
         <v>42</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H10" t="n">
         <v>16</v>
@@ -1761,13 +1761,13 @@
         <v>22</v>
       </c>
       <c r="J10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
         <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M10" t="n">
         <v>20</v>
@@ -1785,13 +1785,13 @@
         <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
       </c>
       <c r="T10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="U10" t="n">
         <v>22</v>
@@ -1818,28 +1818,28 @@
         <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AE10" t="n">
         <v>4</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.516</v>
+        <v>0.531</v>
       </c>
       <c r="AK10" t="n">
         <v>11</v>
@@ -1852,38 +1852,38 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>526:54</t>
+          <t>541:08</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>147.68</v>
+        <v>150.68</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.66</v>
+        <v>0.656</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.672</v>
+        <v>0.668</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.226</v>
+        <v>1.221</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.128</v>
+        <v>0.125</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.231</v>
+        <v>1.308</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AY10" t="n">
         <v>0.016</v>
@@ -1896,22 +1896,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" t="n">
         <v>24</v>
       </c>
-      <c r="E11" t="n">
-        <v>37</v>
-      </c>
-      <c r="F11" t="n">
-        <v>23</v>
-      </c>
       <c r="G11" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H11" t="n">
         <v>13</v>
@@ -1920,19 +1920,19 @@
         <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N11" t="n">
         <v>14</v>
-      </c>
-      <c r="N11" t="n">
-        <v>13</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1944,19 +1944,19 @@
         <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S11" t="n">
         <v>16</v>
       </c>
       <c r="T11" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="U11" t="n">
         <v>25</v>
       </c>
       <c r="V11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W11" t="n">
         <v>8</v>
@@ -1965,22 +1965,22 @@
         <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.705</v>
+        <v>0.696</v>
       </c>
       <c r="AB11" t="n">
         <v>5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -1995,57 +1995,57 @@
         <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.312</v>
+        <v>0.278</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.419</v>
+        <v>0.413</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>384:58</t>
+          <t>413:39</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>110.68</v>
+        <v>118.68</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.609</v>
+        <v>0.587</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.615</v>
+        <v>0.594</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.175</v>
+        <v>1.138</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.045</v>
+        <v>0.042</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.135</v>
+        <v>0.125</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.139</v>
+        <v>0.138</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.031</v>
+        <v>0.034</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.184</v>
+        <v>0.18</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="12">
@@ -2055,16 +2055,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E12" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
@@ -2076,46 +2076,46 @@
         <v>21</v>
       </c>
       <c r="I12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J12" t="n">
         <v>28</v>
       </c>
-      <c r="J12" t="n">
-        <v>26</v>
-      </c>
       <c r="K12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="S12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T12" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="U12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="W12" t="n">
         <v>6</v>
@@ -2124,31 +2124,31 @@
         <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Z12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.615</v>
+        <v>0.607</v>
       </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.458</v>
+        <v>0.463</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2170,41 +2170,41 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>363:47</t>
+          <t>402:56</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>131.32</v>
+        <v>147.2</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.616</v>
+        <v>0.621</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.639</v>
+        <v>0.638</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.211</v>
+        <v>1.189</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.053</v>
+        <v>0.068</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.188</v>
+        <v>0.169</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.714</v>
+        <v>2.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.174</v>
+        <v>0.176</v>
       </c>
       <c r="AW12" t="n">
         <v>0.051</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.138</v>
+        <v>0.13</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="13">
@@ -2214,67 +2214,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I13" t="n">
+        <v>36</v>
+      </c>
+      <c r="J13" t="n">
+        <v>52</v>
+      </c>
+      <c r="K13" t="n">
         <v>31</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>17</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>28</v>
+      </c>
+      <c r="R13" t="n">
+        <v>59</v>
+      </c>
+      <c r="S13" t="n">
         <v>49</v>
       </c>
-      <c r="K13" t="n">
-        <v>27</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6</v>
-      </c>
-      <c r="M13" t="n">
-        <v>16</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>27</v>
-      </c>
-      <c r="R13" t="n">
-        <v>56</v>
-      </c>
-      <c r="S13" t="n">
-        <v>44</v>
-      </c>
       <c r="T13" t="n">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W13" t="n">
         <v>21</v>
@@ -2283,84 +2283,84 @@
         <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Z13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.771</v>
+        <v>0.782</v>
       </c>
       <c r="AB13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC13" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.553</v>
+        <v>0.548</v>
       </c>
       <c r="AE13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="AH13" t="n">
         <v>7</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.304</v>
+        <v>0.28</v>
       </c>
       <c r="AK13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AL13" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.398</v>
+        <v>0.391</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>475:50</t>
+          <t>508:58</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>245.64</v>
+        <v>266.84</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.571</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.592</v>
+        <v>0.584</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.054</v>
+        <v>1.046</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.122</v>
+        <v>0.13</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.815</v>
+        <v>1.857</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.249</v>
+        <v>0.253</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="AY13" t="n">
         <v>0.051</v>
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D14" t="n">
         <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H14" t="n">
         <v>18</v>
@@ -2397,37 +2397,37 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K14" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L14" t="n">
         <v>11</v>
       </c>
       <c r="M14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R14" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="S14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T14" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="U14" t="n">
         <v>13</v>
@@ -2454,75 +2454,75 @@
         <v>9</v>
       </c>
       <c r="AC14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.474</v>
+        <v>0.45</v>
       </c>
       <c r="AE14" t="n">
         <v>9</v>
       </c>
       <c r="AF14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>24</v>
       </c>
-      <c r="AG14" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>23</v>
-      </c>
       <c r="AL14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.426</v>
+        <v>0.436</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>519:51</t>
+          <t>542:18</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>164.88</v>
+        <v>169.88</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.55</v>
+        <v>0.545</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.904</v>
+        <v>0.895</v>
       </c>
       <c r="AS14" t="n">
         <v>0.206</v>
       </c>
       <c r="AT14" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.686</v>
+      </c>
+      <c r="AV14" t="n">
         <v>0.151</v>
       </c>
-      <c r="AU14" t="n">
-        <v>2.647</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.153</v>
-      </c>
       <c r="AW14" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.09</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="15">
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="D15" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2550,49 +2550,49 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I15" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R15" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S15" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="T15" t="n">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="U15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="V15" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="W15" t="n">
         <v>8</v>
@@ -2601,22 +2601,22 @@
         <v>6</v>
       </c>
       <c r="Y15" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Z15" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.772</v>
+        <v>0.783</v>
       </c>
       <c r="AB15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="AE15" t="n">
         <v>8</v>
@@ -2647,38 +2647,38 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>532:37</t>
+          <t>563:10</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>230.52</v>
+        <v>241.6</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.671</v>
+        <v>0.675</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.702</v>
+        <v>0.711</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.215</v>
+        <v>1.221</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.134</v>
+        <v>0.141</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.613</v>
+        <v>0.588</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.209</v>
+        <v>0.207</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.221</v>
+        <v>0.217</v>
       </c>
       <c r="AY15" t="n">
         <v>0.02</v>
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -2718,10 +2718,10 @@
         <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
@@ -2733,25 +2733,25 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U16" t="n">
         <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2769,13 +2769,13 @@
         <v>0.696</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>121:27</t>
+          <t>130:44</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>48.72</v>
+        <v>54.72</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5</v>
+        <v>0.516</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.532</v>
+        <v>0.545</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.78</v>
+        <v>0.731</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.267</v>
+        <v>0.329</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.615</v>
+        <v>1.167</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.194</v>
+        <v>0.202</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.022</v>
+        <v>0.04</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.181</v>
+        <v>0.187</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="17">
@@ -2850,16 +2850,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2877,10 +2877,10 @@
         <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M17" t="n">
         <v>3</v>
@@ -2898,43 +2898,43 @@
         <v>16</v>
       </c>
       <c r="R17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S17" t="n">
         <v>26</v>
       </c>
       <c r="T17" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="U17" t="n">
         <v>14</v>
       </c>
       <c r="V17" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="W17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X17" t="n">
         <v>3</v>
       </c>
-      <c r="X17" t="n">
-        <v>2</v>
-      </c>
       <c r="Y17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z17" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.784</v>
+        <v>0.789</v>
       </c>
       <c r="AB17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.619</v>
+        <v>0.636</v>
       </c>
       <c r="AE17" t="n">
         <v>7</v>
@@ -2965,38 +2965,38 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>267:19</t>
+          <t>274:11</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.711</v>
+        <v>0.72</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.731</v>
+        <v>0.739</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.274</v>
+        <v>1.291</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.129</v>
+        <v>0.126</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.206</v>
+        <v>0.2</v>
       </c>
       <c r="AU17" t="n">
         <v>0.375</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.224</v>
+        <v>0.223</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.221</v>
+        <v>0.222</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.224</v>
+        <v>0.232</v>
       </c>
       <c r="AY17" t="n">
         <v>0.006</v>
@@ -3009,31 +3009,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K18" t="n">
         <v>19</v>
@@ -3042,7 +3042,7 @@
         <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -3051,49 +3051,49 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R18" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="S18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T18" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="U18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
         <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Z18" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.717</v>
+        <v>0.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.706</v>
+        <v>0.609</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3114,51 +3114,51 @@
         <v>0.833</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.365</v>
+        <v>0.356</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>259:00</t>
+          <t>290:53</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>134.44</v>
+        <v>151.2</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.634</v>
+        <v>0.605</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.654</v>
+        <v>0.629</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.093</v>
+        <v>1.058</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.164</v>
+        <v>0.159</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.188</v>
+        <v>0.193</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.227</v>
+        <v>2.125</v>
       </c>
       <c r="AV18" t="n">
         <v>0.251</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="19">
@@ -3168,61 +3168,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H19" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I19" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J19" t="n">
         <v>32</v>
       </c>
       <c r="K19" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L19" t="n">
         <v>12</v>
       </c>
       <c r="M19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R19" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S19" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T19" t="n">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="U19" t="n">
         <v>20</v>
@@ -3237,13 +3237,13 @@
         <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Z19" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.755</v>
+        <v>0.748</v>
       </c>
       <c r="AB19" t="n">
         <v>13</v>
@@ -3258,66 +3258,66 @@
         <v>5</v>
       </c>
       <c r="AF19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.192</v>
+        <v>0.185</v>
       </c>
       <c r="AH19" t="n">
         <v>10</v>
       </c>
       <c r="AI19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.526</v>
+        <v>0.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.38</v>
+        <v>0.378</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>472:46</t>
+          <t>487:09</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>227.72</v>
+        <v>236.48</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.574</v>
+        <v>0.569</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.612</v>
+        <v>0.606</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.089</v>
+        <v>1.078</v>
       </c>
       <c r="AS19" t="n">
         <v>0.11</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.269</v>
+        <v>0.271</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.28</v>
+        <v>1.231</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.233</v>
+        <v>0.234</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.16</v>
+        <v>0.163</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="20">
@@ -3327,67 +3327,67 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="D20" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E20" t="n">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H20" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I20" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J20" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K20" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="L20" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M20" t="n">
         <v>17</v>
       </c>
       <c r="N20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R20" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="S20" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="T20" t="n">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="U20" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="V20" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="W20" t="n">
         <v>13</v>
@@ -3396,28 +3396,28 @@
         <v>9</v>
       </c>
       <c r="Y20" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="Z20" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.746</v>
+        <v>0.757</v>
       </c>
       <c r="AB20" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AC20" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.533</v>
+        <v>0.547</v>
       </c>
       <c r="AE20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>0.5</v>
@@ -3432,51 +3432,51 @@
         <v>0.167</v>
       </c>
       <c r="AK20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL20" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.108</v>
+        <v>0.125</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>575:06</t>
+          <t>634:30</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>282.12</v>
+        <v>304.64</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.536</v>
+        <v>0.549</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.598</v>
+        <v>0.61</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.017</v>
+        <v>1.047</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.149</v>
+        <v>0.141</v>
       </c>
       <c r="AT20" t="n">
         <v>0.386</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.238</v>
+        <v>1.256</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.237</v>
+        <v>0.231</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.153</v>
+        <v>0.158</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="21">
@@ -3629,7 +3629,7 @@
         <v>0.153</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="AX21" t="n">
         <v>0.149</v>
@@ -3785,13 +3785,13 @@
         <v>0.667</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.216</v>
+        <v>0.215</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.13</v>
+        <v>0.128</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.242</v>
+        <v>0.241</v>
       </c>
       <c r="AY22" t="n">
         <v>0.002</v>
@@ -3804,100 +3804,100 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D23" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F23" t="n">
         <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H23" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I23" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K23" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L23" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>28</v>
+      </c>
+      <c r="R23" t="n">
+        <v>52</v>
+      </c>
+      <c r="S23" t="n">
+        <v>63</v>
+      </c>
+      <c r="T23" t="n">
+        <v>388</v>
+      </c>
+      <c r="U23" t="n">
+        <v>22</v>
+      </c>
+      <c r="V23" t="n">
+        <v>38</v>
+      </c>
+      <c r="W23" t="n">
+        <v>23</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>113</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF23" t="n">
         <v>25</v>
       </c>
-      <c r="Q23" t="n">
-        <v>25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>46</v>
-      </c>
-      <c r="S23" t="n">
-        <v>60</v>
-      </c>
-      <c r="T23" t="n">
-        <v>376</v>
-      </c>
-      <c r="U23" t="n">
-        <v>20</v>
-      </c>
-      <c r="V23" t="n">
-        <v>36</v>
-      </c>
-      <c r="W23" t="n">
-        <v>17</v>
-      </c>
-      <c r="X23" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>109</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>23</v>
-      </c>
       <c r="AG23" t="n">
-        <v>0.435</v>
+        <v>0.44</v>
       </c>
       <c r="AH23" t="n">
         <v>17</v>
@@ -3912,48 +3912,48 @@
         <v>9</v>
       </c>
       <c r="AL23" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>709:33</t>
+          <t>751:03</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>232.84</v>
+        <v>247.16</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.597</v>
+        <v>0.592</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.63</v>
+        <v>0.625</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.125</v>
+        <v>1.109</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.107</v>
+        <v>0.113</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.254</v>
+        <v>0.251</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.68</v>
+        <v>1.571</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.068</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.185</v>
+        <v>0.179</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="24">
@@ -4106,7 +4106,7 @@
         <v>0.141</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="AX24" t="n">
         <v>0</v>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4149,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4281,144 +4281,144 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>2869</v>
+        <v>3046</v>
       </c>
       <c r="D26" t="n">
-        <v>734</v>
+        <v>782</v>
       </c>
       <c r="E26" t="n">
-        <v>1188</v>
+        <v>1276</v>
       </c>
       <c r="F26" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="G26" t="n">
-        <v>820</v>
+        <v>869</v>
       </c>
       <c r="H26" t="n">
-        <v>453</v>
+        <v>486</v>
       </c>
       <c r="I26" t="n">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="J26" t="n">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="K26" t="n">
-        <v>781</v>
+        <v>829</v>
       </c>
       <c r="L26" t="n">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="M26" t="n">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="N26" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="Q26" t="n">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="R26" t="n">
-        <v>656</v>
+        <v>704</v>
       </c>
       <c r="S26" t="n">
-        <v>690</v>
+        <v>732</v>
       </c>
       <c r="T26" t="n">
-        <v>3389</v>
+        <v>3578</v>
       </c>
       <c r="U26" t="n">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="V26" t="n">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="W26" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="X26" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="Y26" t="n">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="Z26" t="n">
-        <v>1134</v>
+        <v>1199</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.762</v>
+        <v>0.766</v>
       </c>
       <c r="AB26" t="n">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="AC26" t="n">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.537</v>
+        <v>0.533</v>
       </c>
       <c r="AE26" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="AF26" t="n">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.428</v>
+        <v>0.417</v>
       </c>
       <c r="AH26" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.447</v>
+        <v>0.436</v>
       </c>
       <c r="AK26" t="n">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="AL26" t="n">
-        <v>659</v>
+        <v>697</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2651.16</v>
+        <v>2832.08</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.602</v>
+        <v>0.597</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.63</v>
+        <v>0.626</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.082</v>
+        <v>1.076</v>
       </c>
       <c r="AS26" t="n">
         <v>0.141</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.408</v>
+        <v>1.384</v>
       </c>
       <c r="AV26" t="n">
         <v>0.2</v>
@@ -4427,7 +4427,7 @@
         <v>0.057</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4440,150 +4440,150 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2618</v>
+        <v>2815</v>
       </c>
       <c r="D27" t="n">
-        <v>645</v>
+        <v>689</v>
       </c>
       <c r="E27" t="n">
-        <v>1136</v>
+        <v>1207</v>
       </c>
       <c r="F27" t="n">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="G27" t="n">
-        <v>799</v>
+        <v>862</v>
       </c>
       <c r="H27" t="n">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="I27" t="n">
-        <v>635</v>
+        <v>683</v>
       </c>
       <c r="J27" t="n">
-        <v>524</v>
+        <v>557</v>
       </c>
       <c r="K27" t="n">
-        <v>695</v>
+        <v>751</v>
       </c>
       <c r="L27" t="n">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="M27" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="N27" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="Q27" t="n">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="R27" t="n">
-        <v>693</v>
+        <v>736</v>
       </c>
       <c r="S27" t="n">
-        <v>649</v>
+        <v>697</v>
       </c>
       <c r="T27" t="n">
-        <v>2841</v>
+        <v>3076</v>
       </c>
       <c r="U27" t="n">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="V27" t="n">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="W27" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="X27" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="Y27" t="n">
-        <v>890</v>
+        <v>952</v>
       </c>
       <c r="Z27" t="n">
-        <v>1160</v>
+        <v>1237</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.767</v>
+        <v>0.77</v>
       </c>
       <c r="AB27" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="AC27" t="n">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.465</v>
+        <v>0.474</v>
       </c>
       <c r="AE27" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="AF27" t="n">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="AH27" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="AI27" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.347</v>
+        <v>0.356</v>
       </c>
       <c r="AK27" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="AL27" t="n">
-        <v>609</v>
+        <v>657</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2627.4</v>
+        <v>2812.52</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.549</v>
+        <v>0.552</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.591</v>
+        <v>0.594</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.996</v>
+        <v>1.001</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.255</v>
+        <v>0.257</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.269</v>
+        <v>1.257</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="AX27" t="n">
         <v>0.143</v>
@@ -4656,156 +4656,156 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>13.2</v>
+        <v>13.344</v>
       </c>
       <c r="D29" t="n">
-        <v>2.567</v>
+        <v>2.594</v>
       </c>
       <c r="E29" t="n">
-        <v>4.667</v>
+        <v>4.812</v>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>2.094</v>
       </c>
       <c r="G29" t="n">
-        <v>4.667</v>
+        <v>4.656</v>
       </c>
       <c r="H29" t="n">
-        <v>1.767</v>
+        <v>1.875</v>
       </c>
       <c r="I29" t="n">
-        <v>2.067</v>
+        <v>2.188</v>
       </c>
       <c r="J29" t="n">
-        <v>1.833</v>
+        <v>1.844</v>
       </c>
       <c r="K29" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2</v>
+        <v>0.219</v>
       </c>
       <c r="M29" t="n">
-        <v>1.033</v>
+        <v>1.094</v>
       </c>
       <c r="N29" t="n">
-        <v>0.433</v>
+        <v>0.406</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.467</v>
+        <v>1.469</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.467</v>
+        <v>1.469</v>
       </c>
       <c r="R29" t="n">
-        <v>2.1</v>
+        <v>2.125</v>
       </c>
       <c r="S29" t="n">
-        <v>2.533</v>
+        <v>2.562</v>
       </c>
       <c r="T29" t="n">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="U29" t="n">
-        <v>1.567</v>
+        <v>1.688</v>
       </c>
       <c r="V29" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="W29" t="n">
-        <v>0.633</v>
+        <v>0.75</v>
       </c>
       <c r="X29" t="n">
-        <v>0.3</v>
+        <v>0.375</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.7</v>
+        <v>2.812</v>
       </c>
       <c r="AA29" t="n">
         <v>0.889</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.4</v>
+        <v>0.469</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>1.062</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.4</v>
+        <v>0.441</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.533</v>
+        <v>1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>3.033</v>
+        <v>3.125</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.505</v>
+        <v>0.48</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.3</v>
+        <v>0.344</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.45</v>
+        <v>0.458</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>4</v>
+        <v>3.906</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>11.709</v>
+        <v>11.9</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.612</v>
+        <v>0.606</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.644</v>
+        <v>0.64</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.127</v>
+        <v>1.121</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.125</v>
+        <v>0.123</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.189</v>
+        <v>0.198</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.25</v>
+        <v>1.255</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.24</v>
+        <v>0.241</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="30">
@@ -4815,43 +4815,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>4.469</v>
+        <v>4.559</v>
       </c>
       <c r="D30" t="n">
-        <v>0.75</v>
+        <v>0.735</v>
       </c>
       <c r="E30" t="n">
-        <v>1.375</v>
+        <v>1.5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.875</v>
+        <v>0.912</v>
       </c>
       <c r="G30" t="n">
-        <v>2.031</v>
+        <v>2.088</v>
       </c>
       <c r="H30" t="n">
-        <v>0.344</v>
+        <v>0.353</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="J30" t="n">
-        <v>1.781</v>
+        <v>1.794</v>
       </c>
       <c r="K30" t="n">
-        <v>1.062</v>
+        <v>1.147</v>
       </c>
       <c r="L30" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="M30" t="n">
-        <v>0.625</v>
+        <v>0.706</v>
       </c>
       <c r="N30" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4863,108 +4863,108 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.969</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="U30" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="V30" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="W30" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="X30" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.281</v>
+        <v>1.294</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.61</v>
+        <v>0.614</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.375</v>
+        <v>0.441</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.583</v>
+        <v>0.467</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.219</v>
+        <v>0.294</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.429</v>
+        <v>0.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.333</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.853</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.844</v>
+        <v>1.912</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.441</v>
+        <v>0.446</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>4.626</v>
+        <v>4.821</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.606</v>
+        <v>0.586</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.616</v>
+        <v>0.597</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.966</v>
+        <v>0.946</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.216</v>
+        <v>0.207</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.101</v>
+        <v>0.098</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.781</v>
+        <v>1.794</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.099</v>
+        <v>0.103</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="31">
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="n">
-        <v>6.962</v>
+        <v>6.815</v>
       </c>
       <c r="D31" t="n">
-        <v>1.615</v>
+        <v>1.556</v>
       </c>
       <c r="E31" t="n">
-        <v>2.115</v>
+        <v>2.111</v>
       </c>
       <c r="F31" t="n">
-        <v>1.038</v>
+        <v>1.037</v>
       </c>
       <c r="G31" t="n">
-        <v>2.692</v>
+        <v>2.63</v>
       </c>
       <c r="H31" t="n">
-        <v>0.615</v>
+        <v>0.593</v>
       </c>
       <c r="I31" t="n">
-        <v>0.846</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.615</v>
+        <v>0.63</v>
       </c>
       <c r="K31" t="n">
-        <v>1.423</v>
+        <v>1.37</v>
       </c>
       <c r="L31" t="n">
-        <v>0.538</v>
+        <v>0.593</v>
       </c>
       <c r="M31" t="n">
-        <v>0.769</v>
+        <v>0.741</v>
       </c>
       <c r="N31" t="n">
-        <v>0.115</v>
+        <v>0.111</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="R31" t="n">
-        <v>2.231</v>
+        <v>2.185</v>
       </c>
       <c r="S31" t="n">
-        <v>0.962</v>
+        <v>0.926</v>
       </c>
       <c r="T31" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="U31" t="n">
-        <v>0.846</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="V31" t="n">
-        <v>0.615</v>
+        <v>0.593</v>
       </c>
       <c r="W31" t="n">
-        <v>0.385</v>
+        <v>0.37</v>
       </c>
       <c r="X31" t="n">
-        <v>0.192</v>
+        <v>0.185</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.885</v>
+        <v>1.815</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.154</v>
+        <v>2.074</v>
       </c>
       <c r="AA31" t="n">
         <v>0.875</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.192</v>
+        <v>0.185</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.385</v>
+        <v>0.407</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.154</v>
+        <v>0.148</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.423</v>
+        <v>0.444</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.615</v>
+        <v>0.63</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.192</v>
+        <v>1.185</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.516</v>
+        <v>0.531</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.423</v>
+        <v>0.407</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.5</v>
+        <v>1.444</v>
       </c>
       <c r="AM31" t="n">
         <v>0.282</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>5.68</v>
+        <v>5.581</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.66</v>
+        <v>0.656</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.672</v>
+        <v>0.668</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.226</v>
+        <v>1.221</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.128</v>
+        <v>0.125</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.231</v>
+        <v>1.308</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="32">
@@ -5133,153 +5133,153 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>7.222</v>
+        <v>6.75</v>
       </c>
       <c r="D32" t="n">
-        <v>1.333</v>
+        <v>1.25</v>
       </c>
       <c r="E32" t="n">
-        <v>2.056</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>1.278</v>
+        <v>1.2</v>
       </c>
       <c r="G32" t="n">
-        <v>3.278</v>
+        <v>3.2</v>
       </c>
       <c r="H32" t="n">
-        <v>0.722</v>
+        <v>0.65</v>
       </c>
       <c r="I32" t="n">
-        <v>1.222</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.389</v>
+        <v>0.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.222</v>
+        <v>3.05</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0.778</v>
+        <v>0.75</v>
       </c>
       <c r="N32" t="n">
-        <v>0.722</v>
+        <v>0.7</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.278</v>
+        <v>0.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.278</v>
+        <v>0.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.556</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>0.889</v>
+        <v>0.8</v>
       </c>
       <c r="T32" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="U32" t="n">
-        <v>1.389</v>
+        <v>1.25</v>
       </c>
       <c r="V32" t="n">
-        <v>1.111</v>
+        <v>1.1</v>
       </c>
       <c r="W32" t="n">
-        <v>0.444</v>
+        <v>0.4</v>
       </c>
       <c r="X32" t="n">
-        <v>0.167</v>
+        <v>0.15</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.722</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.444</v>
+        <v>2.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.705</v>
+        <v>0.696</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.278</v>
+        <v>0.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.556</v>
+        <v>0.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.056</v>
+        <v>0.05</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.278</v>
+        <v>0.25</v>
       </c>
       <c r="AG32" t="n">
         <v>0.2</v>
       </c>
       <c r="AH32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>0.278</v>
       </c>
-      <c r="AI32" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.313</v>
-      </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.389</v>
+        <v>2.3</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.419</v>
+        <v>0.413</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>6.149</v>
+        <v>5.934</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.609</v>
+        <v>0.587</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.615</v>
+        <v>0.594</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.175</v>
+        <v>1.138</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.045</v>
+        <v>0.042</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.135</v>
+        <v>0.125</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.139</v>
+        <v>0.138</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.031</v>
+        <v>0.034</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.184</v>
+        <v>0.18</v>
       </c>
       <c r="AY32" t="n">
         <v>0.013</v>
@@ -5292,100 +5292,100 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C33" t="n">
-        <v>6.625</v>
+        <v>6.731</v>
       </c>
       <c r="D33" t="n">
-        <v>2.375</v>
+        <v>2.5</v>
       </c>
       <c r="E33" t="n">
-        <v>3.958</v>
+        <v>4.115</v>
       </c>
       <c r="F33" t="n">
-        <v>0.333</v>
+        <v>0.308</v>
       </c>
       <c r="G33" t="n">
-        <v>0.708</v>
+        <v>0.654</v>
       </c>
       <c r="H33" t="n">
-        <v>0.875</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>1.167</v>
+        <v>1.154</v>
       </c>
       <c r="J33" t="n">
-        <v>1.083</v>
+        <v>1.077</v>
       </c>
       <c r="K33" t="n">
-        <v>1.708</v>
+        <v>1.654</v>
       </c>
       <c r="L33" t="n">
-        <v>0.583</v>
+        <v>0.615</v>
       </c>
       <c r="M33" t="n">
-        <v>0.708</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>0.375</v>
+        <v>0.385</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.292</v>
+        <v>0.385</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.292</v>
+        <v>0.385</v>
       </c>
       <c r="R33" t="n">
-        <v>1.833</v>
+        <v>1.962</v>
       </c>
       <c r="S33" t="n">
-        <v>1.292</v>
+        <v>1.269</v>
       </c>
       <c r="T33" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="U33" t="n">
-        <v>0.75</v>
+        <v>0.769</v>
       </c>
       <c r="V33" t="n">
-        <v>0.25</v>
+        <v>0.462</v>
       </c>
       <c r="W33" t="n">
-        <v>0.25</v>
+        <v>0.231</v>
       </c>
       <c r="X33" t="n">
-        <v>0.125</v>
+        <v>0.115</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.667</v>
+        <v>1.692</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.042</v>
+        <v>2.115</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.667</v>
+        <v>0.654</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.083</v>
+        <v>1.077</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.615</v>
+        <v>0.607</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.917</v>
+        <v>0.962</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>2.077</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.458</v>
+        <v>0.463</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
@@ -5397,48 +5397,48 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.333</v>
+        <v>0.308</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.708</v>
+        <v>0.654</v>
       </c>
       <c r="AM33" t="n">
         <v>0.471</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>5.472</v>
+        <v>5.662</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.616</v>
+        <v>0.621</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.639</v>
+        <v>0.638</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.211</v>
+        <v>1.189</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.053</v>
+        <v>0.068</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.188</v>
+        <v>0.169</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.714</v>
+        <v>2.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.174</v>
+        <v>0.176</v>
       </c>
       <c r="AW33" t="n">
         <v>0.051</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.138</v>
+        <v>0.13</v>
       </c>
       <c r="AY33" t="n">
         <v>0.036</v>
@@ -5451,153 +5451,153 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>8.632999999999999</v>
+        <v>8.718999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>1.5</v>
+        <v>1.562</v>
       </c>
       <c r="E34" t="n">
-        <v>2.633</v>
+        <v>2.75</v>
       </c>
       <c r="F34" t="n">
-        <v>1.6</v>
+        <v>1.562</v>
       </c>
       <c r="G34" t="n">
-        <v>4.2</v>
+        <v>4.219</v>
       </c>
       <c r="H34" t="n">
-        <v>0.833</v>
+        <v>0.906</v>
       </c>
       <c r="I34" t="n">
-        <v>1.033</v>
+        <v>1.125</v>
       </c>
       <c r="J34" t="n">
-        <v>1.633</v>
+        <v>1.625</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9</v>
+        <v>0.969</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="M34" t="n">
-        <v>0.533</v>
+        <v>0.531</v>
       </c>
       <c r="N34" t="n">
-        <v>0.133</v>
+        <v>0.188</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
       <c r="R34" t="n">
-        <v>1.867</v>
+        <v>1.844</v>
       </c>
       <c r="S34" t="n">
-        <v>1.467</v>
+        <v>1.531</v>
       </c>
       <c r="T34" t="n">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="U34" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>0.4</v>
+        <v>0.438</v>
       </c>
       <c r="W34" t="n">
-        <v>0.7</v>
+        <v>0.656</v>
       </c>
       <c r="X34" t="n">
-        <v>0.367</v>
+        <v>0.344</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.233</v>
+        <v>1.344</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.6</v>
+        <v>1.719</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.771</v>
+        <v>0.782</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.7</v>
+        <v>0.719</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.267</v>
+        <v>1.312</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.553</v>
+        <v>0.548</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.8</v>
+        <v>0.844</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.233</v>
+        <v>0.219</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.767</v>
+        <v>0.781</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.304</v>
+        <v>0.28</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.367</v>
+        <v>1.344</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.433</v>
+        <v>3.438</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.398</v>
+        <v>0.391</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>8.188000000000001</v>
+        <v>8.339</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.571</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.592</v>
+        <v>0.584</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.054</v>
+        <v>1.046</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.122</v>
+        <v>0.13</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.815</v>
+        <v>1.857</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.249</v>
+        <v>0.253</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="AY34" t="n">
         <v>0.055</v>
@@ -5610,67 +5610,67 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C35" t="n">
-        <v>6.478</v>
+        <v>6.333</v>
       </c>
       <c r="D35" t="n">
-        <v>1.348</v>
+        <v>1.292</v>
       </c>
       <c r="E35" t="n">
-        <v>2.652</v>
+        <v>2.625</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>2.522</v>
+        <v>2.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0.783</v>
+        <v>0.75</v>
       </c>
       <c r="I35" t="n">
-        <v>1.174</v>
+        <v>1.125</v>
       </c>
       <c r="J35" t="n">
-        <v>3.913</v>
+        <v>3.917</v>
       </c>
       <c r="K35" t="n">
-        <v>2.043</v>
+        <v>2.083</v>
       </c>
       <c r="L35" t="n">
-        <v>0.478</v>
+        <v>0.458</v>
       </c>
       <c r="M35" t="n">
-        <v>0.696</v>
+        <v>0.708</v>
       </c>
       <c r="N35" t="n">
-        <v>0.13</v>
+        <v>0.167</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.478</v>
+        <v>1.458</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.478</v>
+        <v>1.458</v>
       </c>
       <c r="R35" t="n">
-        <v>1.826</v>
+        <v>1.875</v>
       </c>
       <c r="S35" t="n">
-        <v>2.087</v>
+        <v>2.042</v>
       </c>
       <c r="T35" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="U35" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="V35" t="n">
-        <v>0.261</v>
+        <v>0.25</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.348</v>
+        <v>1.292</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.957</v>
+        <v>1.875</v>
       </c>
       <c r="AA35" t="n">
         <v>0.6889999999999999</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.391</v>
+        <v>0.375</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.826</v>
+        <v>0.833</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.474</v>
+        <v>0.45</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.391</v>
+        <v>0.375</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.043</v>
+        <v>1.042</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.375</v>
+        <v>0.36</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.174</v>
+        <v>0.208</v>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
@@ -5718,48 +5718,48 @@
         <v>1</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.348</v>
+        <v>2.292</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.426</v>
+        <v>0.436</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>7.169</v>
+        <v>7.078</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.55</v>
+        <v>0.545</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.904</v>
+        <v>0.895</v>
       </c>
       <c r="AS35" t="n">
         <v>0.206</v>
       </c>
       <c r="AT35" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2.686</v>
+      </c>
+      <c r="AV35" t="n">
         <v>0.151</v>
       </c>
-      <c r="AU35" t="n">
-        <v>2.647</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0.153</v>
-      </c>
       <c r="AW35" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="36">
@@ -5769,97 +5769,97 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>8.75</v>
+        <v>8.676</v>
       </c>
       <c r="D36" t="n">
-        <v>3.188</v>
+        <v>3.118</v>
       </c>
       <c r="E36" t="n">
-        <v>4.688</v>
+        <v>4.559</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="H36" t="n">
-        <v>2.375</v>
+        <v>2.441</v>
       </c>
       <c r="I36" t="n">
-        <v>3.375</v>
+        <v>3.382</v>
       </c>
       <c r="J36" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>2.941</v>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>1.235</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="N36" t="n">
-        <v>0.844</v>
+        <v>0.824</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.719</v>
+        <v>1.706</v>
       </c>
       <c r="S36" t="n">
-        <v>3.281</v>
+        <v>3.235</v>
       </c>
       <c r="T36" t="n">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="U36" t="n">
-        <v>0.875</v>
+        <v>0.882</v>
       </c>
       <c r="V36" t="n">
-        <v>1.406</v>
+        <v>1.441</v>
       </c>
       <c r="W36" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="X36" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="Y36" t="n">
-        <v>4.656</v>
+        <v>4.676</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.031</v>
+        <v>5.971</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.772</v>
+        <v>0.783</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.656</v>
+        <v>0.647</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.375</v>
+        <v>1.353</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.656</v>
+        <v>0.618</v>
       </c>
       <c r="AG36" t="n">
         <v>0.381</v>
@@ -5877,45 +5877,45 @@
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AM36" t="n">
         <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>7.204</v>
+        <v>7.106</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.671</v>
+        <v>0.675</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.702</v>
+        <v>0.711</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.215</v>
+        <v>1.221</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.134</v>
+        <v>0.141</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.613</v>
+        <v>0.588</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.209</v>
+        <v>0.207</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.221</v>
+        <v>0.217</v>
       </c>
       <c r="AY36" t="n">
         <v>0.02</v>
@@ -5928,67 +5928,67 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C37" t="n">
-        <v>5.429</v>
+        <v>4.444</v>
       </c>
       <c r="D37" t="n">
-        <v>1.714</v>
+        <v>1.444</v>
       </c>
       <c r="E37" t="n">
-        <v>2.857</v>
+        <v>2.333</v>
       </c>
       <c r="F37" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="G37" t="n">
-        <v>1.429</v>
+        <v>1.111</v>
       </c>
       <c r="H37" t="n">
-        <v>1.143</v>
+        <v>0.889</v>
       </c>
       <c r="I37" t="n">
-        <v>1.857</v>
+        <v>1.444</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>2.333</v>
       </c>
       <c r="K37" t="n">
-        <v>2.571</v>
+        <v>2.222</v>
       </c>
       <c r="L37" t="n">
-        <v>0.286</v>
+        <v>0.444</v>
       </c>
       <c r="M37" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="N37" t="n">
-        <v>0.143</v>
+        <v>0.111</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.857</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.857</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>1.857</v>
+        <v>1.556</v>
       </c>
       <c r="S37" t="n">
-        <v>2.571</v>
+        <v>2.111</v>
       </c>
       <c r="T37" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U37" t="n">
-        <v>0.857</v>
+        <v>0.667</v>
       </c>
       <c r="V37" t="n">
-        <v>0.429</v>
+        <v>0.556</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -5997,28 +5997,28 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.286</v>
+        <v>1.778</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.286</v>
+        <v>2.556</v>
       </c>
       <c r="AA37" t="n">
         <v>0.696</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.857</v>
+        <v>0.778</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.143</v>
+        <v>0.111</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="AG37" t="n">
         <v>0.25</v>
@@ -6033,51 +6033,51 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.429</v>
+        <v>1.111</v>
       </c>
       <c r="AM37" t="n">
         <v>0.2</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>6.96</v>
+        <v>6.08</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.5</v>
+        <v>0.516</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.532</v>
+        <v>0.545</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.78</v>
+        <v>0.731</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.267</v>
+        <v>0.329</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.615</v>
+        <v>1.167</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.194</v>
+        <v>0.202</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.022</v>
+        <v>0.04</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.181</v>
+        <v>0.187</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.097</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="38">
@@ -6087,16 +6087,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C38" t="n">
-        <v>4.938</v>
+        <v>4.97</v>
       </c>
       <c r="D38" t="n">
-        <v>2.156</v>
+        <v>2.182</v>
       </c>
       <c r="E38" t="n">
-        <v>3.031</v>
+        <v>3.03</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -6105,79 +6105,79 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.625</v>
+        <v>0.606</v>
       </c>
       <c r="I38" t="n">
-        <v>0.781</v>
+        <v>0.758</v>
       </c>
       <c r="J38" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="K38" t="n">
-        <v>1.531</v>
+        <v>1.576</v>
       </c>
       <c r="L38" t="n">
-        <v>1.406</v>
+        <v>1.424</v>
       </c>
       <c r="M38" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="R38" t="n">
-        <v>1.094</v>
+        <v>1.091</v>
       </c>
       <c r="S38" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.788</v>
       </c>
       <c r="T38" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="U38" t="n">
-        <v>0.438</v>
+        <v>0.424</v>
       </c>
       <c r="V38" t="n">
-        <v>1.656</v>
+        <v>1.727</v>
       </c>
       <c r="W38" t="n">
-        <v>0.094</v>
+        <v>0.152</v>
       </c>
       <c r="X38" t="n">
-        <v>0.062</v>
+        <v>0.091</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.156</v>
+        <v>2.152</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.75</v>
+        <v>2.727</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.784</v>
+        <v>0.789</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.406</v>
+        <v>0.424</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.656</v>
+        <v>0.667</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.619</v>
+        <v>0.636</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.219</v>
+        <v>0.212</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.406</v>
+        <v>0.394</v>
       </c>
       <c r="AG38" t="n">
         <v>0.538</v>
@@ -6202,38 +6202,38 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>3.875</v>
+        <v>3.848</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.711</v>
+        <v>0.72</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.731</v>
+        <v>0.739</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.274</v>
+        <v>1.291</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.129</v>
+        <v>0.126</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.206</v>
+        <v>0.2</v>
       </c>
       <c r="AU38" t="n">
         <v>0.375</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.224</v>
+        <v>0.223</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.221</v>
+        <v>0.222</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.224</v>
+        <v>0.232</v>
       </c>
       <c r="AY38" t="n">
         <v>0.006</v>
@@ -6246,156 +6246,156 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C39" t="n">
-        <v>11.308</v>
+        <v>10.667</v>
       </c>
       <c r="D39" t="n">
-        <v>2.154</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.308</v>
+        <v>3.267</v>
       </c>
       <c r="F39" t="n">
-        <v>1.846</v>
+        <v>1.733</v>
       </c>
       <c r="G39" t="n">
-        <v>4.462</v>
+        <v>4.333</v>
       </c>
       <c r="H39" t="n">
-        <v>1.462</v>
+        <v>1.467</v>
       </c>
       <c r="I39" t="n">
         <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>3.769</v>
+        <v>3.4</v>
       </c>
       <c r="K39" t="n">
-        <v>1.462</v>
+        <v>1.267</v>
       </c>
       <c r="L39" t="n">
-        <v>0.385</v>
+        <v>0.333</v>
       </c>
       <c r="M39" t="n">
-        <v>0.615</v>
+        <v>0.667</v>
       </c>
       <c r="N39" t="n">
-        <v>0.308</v>
+        <v>0.267</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.692</v>
+        <v>1.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.692</v>
+        <v>1.6</v>
       </c>
       <c r="R39" t="n">
-        <v>2.385</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.462</v>
+        <v>2.267</v>
       </c>
       <c r="T39" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="U39" t="n">
-        <v>1.308</v>
+        <v>1.267</v>
       </c>
       <c r="V39" t="n">
-        <v>0.846</v>
+        <v>0.733</v>
       </c>
       <c r="W39" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="X39" t="n">
-        <v>0.462</v>
+        <v>0.467</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.538</v>
+        <v>2.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.538</v>
+        <v>3.333</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.717</v>
+        <v>0.72</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.923</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.308</v>
+        <v>1.533</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.706</v>
+        <v>0.609</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.154</v>
+        <v>0.133</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.462</v>
+        <v>0.4</v>
       </c>
       <c r="AG39" t="n">
         <v>0.333</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.385</v>
+        <v>0.333</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.462</v>
+        <v>0.4</v>
       </c>
       <c r="AJ39" t="n">
         <v>0.833</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.462</v>
+        <v>1.4</v>
       </c>
       <c r="AL39" t="n">
-        <v>4</v>
+        <v>3.933</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.365</v>
+        <v>0.356</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>10.342</v>
+        <v>10.08</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.634</v>
+        <v>0.605</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.654</v>
+        <v>0.629</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.093</v>
+        <v>1.058</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.164</v>
+        <v>0.159</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.188</v>
+        <v>0.193</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.227</v>
+        <v>2.125</v>
       </c>
       <c r="AV39" t="n">
         <v>0.251</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.131</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="40">
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" t="n">
-        <v>12.4</v>
+        <v>12.143</v>
       </c>
       <c r="D40" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="E40" t="n">
-        <v>4.25</v>
+        <v>4.143</v>
       </c>
       <c r="F40" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="G40" t="n">
-        <v>4.5</v>
+        <v>4.476</v>
       </c>
       <c r="H40" t="n">
-        <v>2.35</v>
+        <v>2.333</v>
       </c>
       <c r="I40" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="J40" t="n">
-        <v>1.6</v>
+        <v>1.524</v>
       </c>
       <c r="K40" t="n">
-        <v>3.1</v>
+        <v>3.095</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="M40" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.857</v>
+      </c>
+      <c r="T40" t="n">
+        <v>274</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="V40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T40" t="n">
-        <v>265</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.05</v>
-      </c>
       <c r="W40" t="n">
-        <v>1.2</v>
+        <v>1.143</v>
       </c>
       <c r="X40" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.7</v>
+        <v>3.667</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.9</v>
+        <v>4.905</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.755</v>
+        <v>0.748</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.65</v>
+        <v>0.619</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.2</v>
+        <v>1.143</v>
       </c>
       <c r="AD40" t="n">
         <v>0.542</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.25</v>
+        <v>0.238</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.3</v>
+        <v>1.286</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.192</v>
+        <v>0.185</v>
       </c>
       <c r="AH40" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AI40" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.526</v>
-      </c>
       <c r="AK40" t="n">
-        <v>1.35</v>
+        <v>1.333</v>
       </c>
       <c r="AL40" t="n">
-        <v>3.55</v>
+        <v>3.524</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.38</v>
+        <v>0.378</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>23:38</t>
+          <t>23:11</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>11.386</v>
+        <v>11.261</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.574</v>
+        <v>0.569</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.612</v>
+        <v>0.606</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.089</v>
+        <v>1.078</v>
       </c>
       <c r="AS40" t="n">
         <v>0.11</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.269</v>
+        <v>0.271</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.28</v>
+        <v>1.231</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.233</v>
+        <v>0.234</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.16</v>
+        <v>0.163</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.056</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="41">
@@ -6564,156 +6564,156 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C41" t="n">
-        <v>10.25</v>
+        <v>10.633</v>
       </c>
       <c r="D41" t="n">
-        <v>3.5</v>
+        <v>3.633</v>
       </c>
       <c r="E41" t="n">
-        <v>5.5</v>
+        <v>5.633</v>
       </c>
       <c r="F41" t="n">
-        <v>0.179</v>
+        <v>0.2</v>
       </c>
       <c r="G41" t="n">
-        <v>1.536</v>
+        <v>1.533</v>
       </c>
       <c r="H41" t="n">
-        <v>2.714</v>
+        <v>2.767</v>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>3.533</v>
       </c>
       <c r="J41" t="n">
-        <v>1.857</v>
+        <v>1.8</v>
       </c>
       <c r="K41" t="n">
-        <v>2.571</v>
+        <v>2.733</v>
       </c>
       <c r="L41" t="n">
-        <v>0.964</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.607</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>0.821</v>
+        <v>0.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.5</v>
+        <v>1.433</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.5</v>
+        <v>1.433</v>
       </c>
       <c r="R41" t="n">
-        <v>2.143</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
-        <v>4.179</v>
+        <v>4.133</v>
       </c>
       <c r="T41" t="n">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="U41" t="n">
-        <v>0.964</v>
+        <v>1.1</v>
       </c>
       <c r="V41" t="n">
-        <v>1.179</v>
+        <v>1.333</v>
       </c>
       <c r="W41" t="n">
-        <v>0.464</v>
+        <v>0.433</v>
       </c>
       <c r="X41" t="n">
-        <v>0.321</v>
+        <v>0.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>5.036</v>
+        <v>5.1</v>
       </c>
       <c r="Z41" t="n">
-        <v>6.75</v>
+        <v>6.733</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.746</v>
+        <v>0.757</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.857</v>
+        <v>0.967</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.607</v>
+        <v>1.767</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.533</v>
+        <v>0.547</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.321</v>
+        <v>0.333</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="AG41" t="n">
         <v>0.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AJ41" t="n">
         <v>0.167</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.143</v>
+        <v>0.167</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.321</v>
+        <v>1.333</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.108</v>
+        <v>0.125</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>10.076</v>
+        <v>10.155</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.536</v>
+        <v>0.549</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.598</v>
+        <v>0.61</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.017</v>
+        <v>1.047</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.149</v>
+        <v>0.141</v>
       </c>
       <c r="AT41" t="n">
         <v>0.386</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.238</v>
+        <v>1.256</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.237</v>
+        <v>0.231</v>
       </c>
       <c r="AW41" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AY41" t="n">
         <v>0.062</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0.064</v>
       </c>
     </row>
     <row r="42">
@@ -6866,7 +6866,7 @@
         <v>0.153</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="AX42" t="n">
         <v>0.149</v>
@@ -7022,13 +7022,13 @@
         <v>0.667</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.216</v>
+        <v>0.215</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.13</v>
+        <v>0.128</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.242</v>
+        <v>0.241</v>
       </c>
       <c r="AY43" t="n">
         <v>0.006</v>
@@ -7041,156 +7041,156 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C44" t="n">
-        <v>8.452</v>
+        <v>8.303000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>2.226</v>
+        <v>2.242</v>
       </c>
       <c r="E44" t="n">
-        <v>3.452</v>
+        <v>3.455</v>
       </c>
       <c r="F44" t="n">
-        <v>0.839</v>
+        <v>0.788</v>
       </c>
       <c r="G44" t="n">
-        <v>2.387</v>
+        <v>2.333</v>
       </c>
       <c r="H44" t="n">
-        <v>1.484</v>
+        <v>1.455</v>
       </c>
       <c r="I44" t="n">
-        <v>1.968</v>
+        <v>1.939</v>
       </c>
       <c r="J44" t="n">
-        <v>1.355</v>
+        <v>1.333</v>
       </c>
       <c r="K44" t="n">
-        <v>3.452</v>
+        <v>3.333</v>
       </c>
       <c r="L44" t="n">
-        <v>1.194</v>
+        <v>1.212</v>
       </c>
       <c r="M44" t="n">
-        <v>0.871</v>
+        <v>0.879</v>
       </c>
       <c r="N44" t="n">
-        <v>0.419</v>
+        <v>0.455</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.806</v>
+        <v>0.848</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.806</v>
+        <v>0.848</v>
       </c>
       <c r="R44" t="n">
-        <v>1.484</v>
+        <v>1.576</v>
       </c>
       <c r="S44" t="n">
-        <v>1.935</v>
+        <v>1.909</v>
       </c>
       <c r="T44" t="n">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="U44" t="n">
-        <v>0.645</v>
+        <v>0.667</v>
       </c>
       <c r="V44" t="n">
-        <v>1.161</v>
+        <v>1.152</v>
       </c>
       <c r="W44" t="n">
-        <v>0.548</v>
+        <v>0.697</v>
       </c>
       <c r="X44" t="n">
-        <v>0.387</v>
+        <v>0.455</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.742</v>
+        <v>2.667</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.516</v>
+        <v>3.424</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.645</v>
+        <v>0.697</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.161</v>
+        <v>1.212</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.556</v>
+        <v>0.575</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.323</v>
+        <v>0.333</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.742</v>
+        <v>0.758</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.435</v>
+        <v>0.44</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.548</v>
+        <v>0.515</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="AJ44" t="n">
         <v>0.586</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.29</v>
+        <v>0.273</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.452</v>
+        <v>1.455</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.2</v>
+        <v>0.187</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>22:53</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>7.511</v>
+        <v>7.49</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.597</v>
+        <v>0.592</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.63</v>
+        <v>0.625</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.125</v>
+        <v>1.109</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.107</v>
+        <v>0.113</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.254</v>
+        <v>0.251</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.68</v>
+        <v>1.571</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.068</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.185</v>
+        <v>0.179</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="45">
@@ -7343,7 +7343,7 @@
         <v>0.141</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1.469</v>
+        <v>1.412</v>
       </c>
       <c r="L46" t="n">
-        <v>1.062</v>
+        <v>1.029</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7401,13 +7401,13 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.844</v>
+        <v>0.794</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -7518,144 +7518,144 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C47" t="n">
-        <v>89.65600000000001</v>
+        <v>89.58799999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>22.938</v>
+        <v>23</v>
       </c>
       <c r="E47" t="n">
-        <v>37.125</v>
+        <v>37.529</v>
       </c>
       <c r="F47" t="n">
-        <v>9.875</v>
+        <v>9.765000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>25.625</v>
+        <v>25.559</v>
       </c>
       <c r="H47" t="n">
-        <v>14.156</v>
+        <v>14.294</v>
       </c>
       <c r="I47" t="n">
-        <v>19.188</v>
+        <v>19.324</v>
       </c>
       <c r="J47" t="n">
-        <v>16.406</v>
+        <v>16.206</v>
       </c>
       <c r="K47" t="n">
-        <v>24.406</v>
+        <v>24.382</v>
       </c>
       <c r="L47" t="n">
-        <v>8.75</v>
+        <v>8.882</v>
       </c>
       <c r="M47" t="n">
-        <v>7.438</v>
+        <v>7.588</v>
       </c>
       <c r="N47" t="n">
-        <v>4.812</v>
+        <v>4.824</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>11.656</v>
+        <v>11.706</v>
       </c>
       <c r="Q47" t="n">
-        <v>10.812</v>
+        <v>10.912</v>
       </c>
       <c r="R47" t="n">
-        <v>20.5</v>
+        <v>20.706</v>
       </c>
       <c r="S47" t="n">
-        <v>21.562</v>
+        <v>21.529</v>
       </c>
       <c r="T47" t="n">
-        <v>3389</v>
+        <v>3578</v>
       </c>
       <c r="U47" t="n">
-        <v>9.625</v>
+        <v>9.824</v>
       </c>
       <c r="V47" t="n">
-        <v>9.218999999999999</v>
+        <v>9.529</v>
       </c>
       <c r="W47" t="n">
-        <v>4.594</v>
+        <v>4.794</v>
       </c>
       <c r="X47" t="n">
-        <v>2.688</v>
+        <v>2.765</v>
       </c>
       <c r="Y47" t="n">
         <v>27</v>
       </c>
       <c r="Z47" t="n">
-        <v>35.438</v>
+        <v>35.265</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.762</v>
+        <v>0.766</v>
       </c>
       <c r="AB47" t="n">
-        <v>5.719</v>
+        <v>5.941</v>
       </c>
       <c r="AC47" t="n">
-        <v>10.656</v>
+        <v>11.147</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.537</v>
+        <v>0.533</v>
       </c>
       <c r="AE47" t="n">
-        <v>4.375</v>
+        <v>4.353</v>
       </c>
       <c r="AF47" t="n">
-        <v>10.219</v>
+        <v>10.441</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.428</v>
+        <v>0.417</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.25</v>
+        <v>2.206</v>
       </c>
       <c r="AI47" t="n">
-        <v>5.031</v>
+        <v>5.059</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.447</v>
+        <v>0.436</v>
       </c>
       <c r="AK47" t="n">
-        <v>7.625</v>
+        <v>7.559</v>
       </c>
       <c r="AL47" t="n">
-        <v>20.594</v>
+        <v>20.5</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>200:00</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>82.849</v>
+        <v>83.29600000000001</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.602</v>
+        <v>0.597</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.63</v>
+        <v>0.626</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.082</v>
+        <v>1.076</v>
       </c>
       <c r="AS47" t="n">
         <v>0.141</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.408</v>
+        <v>1.384</v>
       </c>
       <c r="AV47" t="n">
         <v>0.2</v>
@@ -7664,7 +7664,7 @@
         <v>0.057</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -7677,153 +7677,153 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
-        <v>81.812</v>
+        <v>82.794</v>
       </c>
       <c r="D48" t="n">
-        <v>20.156</v>
+        <v>20.265</v>
       </c>
       <c r="E48" t="n">
         <v>35.5</v>
       </c>
       <c r="F48" t="n">
-        <v>8.688000000000001</v>
+        <v>8.882</v>
       </c>
       <c r="G48" t="n">
-        <v>24.969</v>
+        <v>25.353</v>
       </c>
       <c r="H48" t="n">
-        <v>15.438</v>
+        <v>15.618</v>
       </c>
       <c r="I48" t="n">
-        <v>19.844</v>
+        <v>20.088</v>
       </c>
       <c r="J48" t="n">
-        <v>16.375</v>
+        <v>16.382</v>
       </c>
       <c r="K48" t="n">
-        <v>21.719</v>
+        <v>22.088</v>
       </c>
       <c r="L48" t="n">
-        <v>8.281000000000001</v>
+        <v>8.471</v>
       </c>
       <c r="M48" t="n">
-        <v>6.125</v>
+        <v>6.265</v>
       </c>
       <c r="N48" t="n">
-        <v>4.781</v>
+        <v>4.824</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>12.906</v>
+        <v>13.029</v>
       </c>
       <c r="Q48" t="n">
-        <v>12.062</v>
+        <v>12.206</v>
       </c>
       <c r="R48" t="n">
-        <v>21.656</v>
+        <v>21.647</v>
       </c>
       <c r="S48" t="n">
-        <v>20.281</v>
+        <v>20.5</v>
       </c>
       <c r="T48" t="n">
-        <v>2841</v>
+        <v>3076</v>
       </c>
       <c r="U48" t="n">
-        <v>9.875</v>
+        <v>10.235</v>
       </c>
       <c r="V48" t="n">
-        <v>7.656</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>4.125</v>
+        <v>4.235</v>
       </c>
       <c r="X48" t="n">
-        <v>2.469</v>
+        <v>2.588</v>
       </c>
       <c r="Y48" t="n">
-        <v>27.812</v>
+        <v>28</v>
       </c>
       <c r="Z48" t="n">
-        <v>36.25</v>
+        <v>36.382</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.767</v>
+        <v>0.77</v>
       </c>
       <c r="AB48" t="n">
-        <v>4.625</v>
+        <v>4.735</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.938000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.465</v>
+        <v>0.474</v>
       </c>
       <c r="AE48" t="n">
-        <v>3.156</v>
+        <v>3.147</v>
       </c>
       <c r="AF48" t="n">
-        <v>9.156000000000001</v>
+        <v>9.206</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.062</v>
+        <v>2.147</v>
       </c>
       <c r="AI48" t="n">
-        <v>5.938</v>
+        <v>6.029</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.347</v>
+        <v>0.356</v>
       </c>
       <c r="AK48" t="n">
-        <v>6.625</v>
+        <v>6.735</v>
       </c>
       <c r="AL48" t="n">
-        <v>19.031</v>
+        <v>19.324</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>200:00</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>82.10599999999999</v>
+        <v>82.721</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.549</v>
+        <v>0.552</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.591</v>
+        <v>0.594</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.996</v>
+        <v>1.001</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.255</v>
+        <v>0.257</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.269</v>
+        <v>1.257</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.198</v>
+        <v>0.199</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.133</v>
+        <v>0.134</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
